--- a/data/raw/portfolio_snapshots/Portfolio_2026.xlsx
+++ b/data/raw/portfolio_snapshots/Portfolio_2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30327"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2c3b54154a9f56a2/Samir/Research/Portfolio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2159" documentId="8_{EDF33660-9B23-4888-B529-2B640994E33F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2DC45205-2A70-4227-8183-CEFBD76FF5B7}"/>
+  <xr:revisionPtr revIDLastSave="2203" documentId="8_{EDF33660-9B23-4888-B529-2B640994E33F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AAB4147E-D7A6-4805-B9FA-0F42DC26AEEB}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="8" activeTab="16" xr2:uid="{D1491BFC-AA9E-4856-B603-CFD392162666}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="18" activeTab="18" xr2:uid="{D1491BFC-AA9E-4856-B603-CFD392162666}"/>
   </bookViews>
   <sheets>
     <sheet name="01Jan26" sheetId="51" r:id="rId1"/>
@@ -30,9 +30,11 @@
     <sheet name="09Jun26" sheetId="88" r:id="rId15"/>
     <sheet name="22Jun26" sheetId="89" r:id="rId16"/>
     <sheet name="01Jul26" sheetId="90" r:id="rId17"/>
-    <sheet name="Sheet1" sheetId="1" r:id="rId18"/>
+    <sheet name="24Jul26" sheetId="91" r:id="rId18"/>
+    <sheet name="28Jul26" sheetId="92" r:id="rId19"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId20"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -53,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="85">
   <si>
     <t>Model Portfolio</t>
   </si>
@@ -76,6 +78,27 @@
     <t>Change</t>
   </si>
   <si>
+    <t>Ashapura</t>
+  </si>
+  <si>
+    <t>AstraMicro</t>
+  </si>
+  <si>
+    <t>Aurionpro</t>
+  </si>
+  <si>
+    <t>Avalon</t>
+  </si>
+  <si>
+    <t>BirlaNu</t>
+  </si>
+  <si>
+    <t>E2E</t>
+  </si>
+  <si>
+    <t>HCG</t>
+  </si>
+  <si>
     <t>Heritage</t>
   </si>
   <si>
@@ -88,13 +111,13 @@
     <t>SuryaRosni</t>
   </si>
   <si>
+    <t>ThomasCook</t>
+  </si>
+  <si>
     <t>VadilalInd</t>
   </si>
   <si>
     <t>VRLLogistics</t>
-  </si>
-  <si>
-    <t>AstraMicro</t>
   </si>
   <si>
     <t>WelEnt</t>
@@ -103,28 +126,7 @@
     <t>ZenTech</t>
   </si>
   <si>
-    <t>ThomasCook</t>
-  </si>
-  <si>
-    <t>Aurionpro</t>
-  </si>
-  <si>
-    <t>Avalon</t>
-  </si>
-  <si>
     <t>LiquidCase</t>
-  </si>
-  <si>
-    <t>E2E</t>
-  </si>
-  <si>
-    <t>BirlaNu</t>
-  </si>
-  <si>
-    <t>HCG</t>
-  </si>
-  <si>
-    <t>Ashapura</t>
   </si>
   <si>
     <t>Add 935@657.76 = 615006</t>
@@ -181,10 +183,10 @@
     <t>Rates of 02-04-2026</t>
   </si>
   <si>
-    <t>Rights Issue 1:17 Ratio at 512</t>
+    <t>Buy 289@512 = 147968</t>
   </si>
   <si>
-    <t>Buy 289@512 = 147968</t>
+    <t>Rights Issue 1:17 Ratio at 512</t>
   </si>
   <si>
     <t>Less 1307</t>
@@ -202,10 +204,10 @@
     <t>Buy 1655@864.33 = 1430466</t>
   </si>
   <si>
-    <t>Sell 767@447.37 = 343132</t>
+    <t>Sell 896@223.98 = 200686</t>
   </si>
   <si>
-    <t>Sell 896@223.98 = 200686</t>
+    <t>Sell 767@447.37 = 343132</t>
   </si>
   <si>
     <t>Less 7827</t>
@@ -229,25 +231,25 @@
     <t>Less 231</t>
   </si>
   <si>
+    <t>Rates of 04-05-2026</t>
+  </si>
+  <si>
+    <t>Sell 130@355.29 = 46188</t>
+  </si>
+  <si>
     <t>InoxWind</t>
   </si>
   <si>
-    <t>Sell 2717@258.8  = 703159</t>
+    <t>Buy 12359@104.89 = 1296335</t>
   </si>
   <si>
-    <t>Sell 130@355.29 = 46188</t>
+    <t>Sell 2717@258.8  = 703159</t>
   </si>
   <si>
     <t>Sell 339@521.43 = 176765</t>
   </si>
   <si>
     <t>Sell 3251</t>
-  </si>
-  <si>
-    <t>Buy 12359@104.89 = 1296335</t>
-  </si>
-  <si>
-    <t>Rates of 04-05-2026</t>
   </si>
   <si>
     <t>Sell 373@373.43 = 129289</t>
@@ -262,19 +264,19 @@
     <t>Split 10:1 so quantity 10 times</t>
   </si>
   <si>
+    <t>Buy 532@525.87 = 279763</t>
+  </si>
+  <si>
     <t>Sell 1507@185.65 = 279774</t>
   </si>
   <si>
-    <t>Buy 532@525.87 = 279763</t>
-  </si>
-  <si>
-    <t>Sell 143@2949.12 = 421724</t>
+    <t>Buy 330@968.16 = 319493</t>
   </si>
   <si>
     <t>Sell 3094@440.83 = 1363928</t>
   </si>
   <si>
-    <t>Buy 330@968.16 = 319493</t>
+    <t>Sell 143@2949.12 = 421724</t>
   </si>
   <si>
     <t>Sell 205@580.5 = 119002</t>
@@ -283,13 +285,31 @@
     <t>Buy 13804</t>
   </si>
   <si>
+    <t>Rates of 10-07-2026</t>
+  </si>
+  <si>
     <t>Sell 937@602.72 = 564748.64</t>
   </si>
   <si>
-    <t>Rates of 10-07-2026</t>
+    <t>Add 4918</t>
   </si>
   <si>
-    <t>Add 4918</t>
+    <t>Rates of 23-07-2026</t>
+  </si>
+  <si>
+    <t>Add 562@643.95 = 358036</t>
+  </si>
+  <si>
+    <t>Sell 3138</t>
+  </si>
+  <si>
+    <t>Rates of 27-07-2026</t>
+  </si>
+  <si>
+    <t>Sell 604@745.93 = 450542</t>
+  </si>
+  <si>
+    <t>Add 3905</t>
   </si>
 </sst>
 </file>
@@ -299,7 +319,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -352,14 +372,10 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -397,7 +413,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -503,7 +519,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -645,7 +661,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -657,20 +673,20 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -679,11 +695,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -703,13 +719,13 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" s="2" customFormat="1">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="B5" s="4">
         <f>2265+463</f>
@@ -731,9 +747,9 @@
       <c r="H5"/>
       <c r="I5"/>
     </row>
-    <row r="6" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" s="2" customFormat="1">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B6" s="4">
         <f>4326+2424</f>
@@ -755,9 +771,9 @@
       <c r="H6"/>
       <c r="I6"/>
     </row>
-    <row r="7" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" s="2" customFormat="1">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B7" s="4">
         <f>448*2+37+403+478+149+306+290</f>
@@ -779,9 +795,9 @@
       <c r="H7"/>
       <c r="I7"/>
     </row>
-    <row r="8" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" s="2" customFormat="1">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B8" s="4">
         <f>1410+2189</f>
@@ -803,9 +819,9 @@
       <c r="H8"/>
       <c r="I8"/>
     </row>
-    <row r="9" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" s="2" customFormat="1">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B9" s="4">
         <f>130+126+33+57+173+130</f>
@@ -827,9 +843,9 @@
       <c r="H9"/>
       <c r="I9"/>
     </row>
-    <row r="10" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" s="2" customFormat="1">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B10" s="4">
         <f>724+289+144+275-367</f>
@@ -851,9 +867,9 @@
       <c r="H10"/>
       <c r="I10"/>
     </row>
-    <row r="11" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" s="2" customFormat="1">
       <c r="A11" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B11" s="4">
         <f>3770+209</f>
@@ -875,9 +891,9 @@
       <c r="H11"/>
       <c r="I11"/>
     </row>
-    <row r="12" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" s="2" customFormat="1">
       <c r="A12" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B12" s="4">
         <f>((840+420)*2+290+562)+3372</f>
@@ -899,9 +915,9 @@
       <c r="H12"/>
       <c r="I12"/>
     </row>
-    <row r="13" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" s="2" customFormat="1">
       <c r="A13" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B13" s="4">
         <f>1280+1280+1280+910+1300+1300+2940+1300-2365+1475-2568</f>
@@ -923,9 +939,9 @@
       <c r="H13"/>
       <c r="I13"/>
     </row>
-    <row r="14" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" s="2" customFormat="1">
       <c r="A14" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B14" s="4">
         <f>(410+205+135+181)*2</f>
@@ -947,9 +963,9 @@
       <c r="H14"/>
       <c r="I14"/>
     </row>
-    <row r="15" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" s="2" customFormat="1">
       <c r="A15" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B15" s="4">
         <f>(1875+937+309+619)*2*2-3720</f>
@@ -971,9 +987,9 @@
       <c r="H15"/>
       <c r="I15"/>
     </row>
-    <row r="16" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" s="2" customFormat="1">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B16" s="4">
         <f>13763+6317+2811+3464+1538</f>
@@ -995,9 +1011,9 @@
       <c r="H16"/>
       <c r="I16"/>
     </row>
-    <row r="17" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" s="2" customFormat="1">
       <c r="A17" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B17" s="4">
         <f>458+115+189</f>
@@ -1019,9 +1035,9 @@
       <c r="H17"/>
       <c r="I17"/>
     </row>
-    <row r="18" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" s="2" customFormat="1">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B18" s="4">
         <f>(3075+1537+1153-53-1428-925-484-459-467-45+2345+1175)*2</f>
@@ -1043,9 +1059,9 @@
       <c r="H18"/>
       <c r="I18"/>
     </row>
-    <row r="19" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" s="2" customFormat="1">
       <c r="A19" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B19" s="4">
         <f>7985+1084+1117+2249-5230-405</f>
@@ -1067,9 +1083,9 @@
       <c r="H19"/>
       <c r="I19" s="3"/>
     </row>
-    <row r="20" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" s="2" customFormat="1">
       <c r="A20" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B20" s="4">
         <f>2592+518+820</f>
@@ -1091,9 +1107,9 @@
       <c r="H20"/>
       <c r="I20"/>
     </row>
-    <row r="21" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" s="2" customFormat="1">
       <c r="A21" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B21" s="4">
         <f>40235+4295+1952-475+9018-12666-5975-9817+11418+1366-3600+5427-7979-25132+6426+17836-15111-2801-1247</f>
@@ -1115,7 +1131,7 @@
       <c r="H21"/>
       <c r="I21"/>
     </row>
-    <row r="22" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" s="2" customFormat="1">
       <c r="A22"/>
       <c r="B22" s="4"/>
       <c r="D22"/>
@@ -1125,7 +1141,7 @@
       <c r="H22"/>
       <c r="I22"/>
     </row>
-    <row r="23" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" s="2" customFormat="1">
       <c r="A23"/>
       <c r="B23" s="4"/>
       <c r="D23">
@@ -1150,21 +1166,21 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J24"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1176,11 +1192,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -1197,13 +1213,13 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" s="2" customFormat="1">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="B5" s="4">
         <f>2265+463+942</f>
@@ -1225,9 +1241,9 @@
       <c r="H5"/>
       <c r="I5"/>
     </row>
-    <row r="6" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" s="2" customFormat="1">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B6" s="4">
         <f>4326+2424</f>
@@ -1249,7 +1265,7 @@
       <c r="H6"/>
       <c r="I6"/>
     </row>
-    <row r="7" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" s="2" customFormat="1">
       <c r="A7" t="s">
         <v>47</v>
       </c>
@@ -1274,9 +1290,9 @@
       <c r="H7"/>
       <c r="I7"/>
     </row>
-    <row r="8" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" s="2" customFormat="1">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B8" s="4">
         <f>448*2+37+403+478+149+306+290</f>
@@ -1298,9 +1314,9 @@
       <c r="H8"/>
       <c r="I8"/>
     </row>
-    <row r="9" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" s="2" customFormat="1">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B9" s="4">
         <f>1410+2189+320+59</f>
@@ -1322,9 +1338,9 @@
       <c r="H9"/>
       <c r="I9"/>
     </row>
-    <row r="10" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" s="2" customFormat="1">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B10" s="4">
         <f>130+126+33+57+173+130</f>
@@ -1346,9 +1362,9 @@
       <c r="H10"/>
       <c r="I10"/>
     </row>
-    <row r="11" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" s="2" customFormat="1">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B11" s="4">
         <f>724+289+144+275-367</f>
@@ -1370,9 +1386,9 @@
       <c r="H11"/>
       <c r="I11"/>
     </row>
-    <row r="12" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" s="2" customFormat="1">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B12" s="4">
         <f>3770+209+935+289</f>
@@ -1394,9 +1410,9 @@
       <c r="H12"/>
       <c r="I12"/>
     </row>
-    <row r="13" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" s="2" customFormat="1">
       <c r="A13" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B13" s="4">
         <f>((840+420)*2+290+562)+3372</f>
@@ -1418,9 +1434,9 @@
       <c r="H13"/>
       <c r="I13"/>
     </row>
-    <row r="14" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" s="2" customFormat="1">
       <c r="A14" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B14" s="4">
         <f>1280+1280+1280+910+1300+1300+2940+1300-2365+1475-2568-1840</f>
@@ -1443,9 +1459,9 @@
       <c r="I14"/>
       <c r="J14" s="5"/>
     </row>
-    <row r="15" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" s="2" customFormat="1">
       <c r="A15" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B15" s="4">
         <f>(410+205+135+181)*2</f>
@@ -1467,9 +1483,9 @@
       <c r="H15"/>
       <c r="I15"/>
     </row>
-    <row r="16" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" s="2" customFormat="1">
       <c r="A16" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B16" s="4">
         <f>(1875+937+309+619)*2*2-3720-1759-2877-896</f>
@@ -1488,14 +1504,14 @@
       </c>
       <c r="F16"/>
       <c r="G16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H16"/>
       <c r="I16"/>
     </row>
-    <row r="17" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" s="2" customFormat="1">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B17" s="4">
         <f>13763+6317+2811+3464+1538</f>
@@ -1517,9 +1533,9 @@
       <c r="H17"/>
       <c r="I17"/>
     </row>
-    <row r="18" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" s="2" customFormat="1">
       <c r="A18" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B18" s="4">
         <f>458+115+189</f>
@@ -1541,9 +1557,9 @@
       <c r="H18"/>
       <c r="I18"/>
     </row>
-    <row r="19" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" s="2" customFormat="1">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B19" s="4">
         <f>(3075+1537+1153-53-1428-925-484-459-467-45+2345+1175)*2</f>
@@ -1565,9 +1581,9 @@
       <c r="H19"/>
       <c r="I19"/>
     </row>
-    <row r="20" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" s="2" customFormat="1">
       <c r="A20" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B20" s="4">
         <f>7985+1084+1117+2249-5230-405-983-767</f>
@@ -1586,13 +1602,13 @@
       </c>
       <c r="F20"/>
       <c r="G20" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H20"/>
     </row>
-    <row r="21" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" s="2" customFormat="1">
       <c r="A21" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B21" s="4">
         <f>2592+518+820</f>
@@ -1614,9 +1630,9 @@
       <c r="H21"/>
       <c r="I21"/>
     </row>
-    <row r="22" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" s="2" customFormat="1">
       <c r="A22" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B22" s="4">
         <f>40235+4295+1952-475+9018-12666-5975-9817+11418+1366-3600+5427-7979-25132+6426+17836-15111-2801-1247-5505-1765+3820-6212+5704-2774+2757-458-1307+3879-7827</f>
@@ -1640,7 +1656,7 @@
       <c r="H22"/>
       <c r="I22"/>
     </row>
-    <row r="23" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" s="2" customFormat="1">
       <c r="A23"/>
       <c r="B23" s="4"/>
       <c r="D23"/>
@@ -1650,7 +1666,7 @@
       <c r="H23"/>
       <c r="I23"/>
     </row>
-    <row r="24" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" s="2" customFormat="1">
       <c r="A24"/>
       <c r="B24" s="4"/>
       <c r="D24">
@@ -1675,21 +1691,21 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1701,11 +1717,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -1722,13 +1738,13 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" s="2" customFormat="1">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="B5" s="4">
         <f>2265+463+942</f>
@@ -1750,9 +1766,9 @@
       <c r="H5"/>
       <c r="I5"/>
     </row>
-    <row r="6" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" s="2" customFormat="1">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B6" s="4">
         <f>4326+2424</f>
@@ -1774,7 +1790,7 @@
       <c r="H6"/>
       <c r="I6"/>
     </row>
-    <row r="7" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" s="2" customFormat="1">
       <c r="A7" t="s">
         <v>47</v>
       </c>
@@ -1797,9 +1813,9 @@
       <c r="H7"/>
       <c r="I7"/>
     </row>
-    <row r="8" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" s="2" customFormat="1">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B8" s="4">
         <f>448*2+37+403+478+149+306+290</f>
@@ -1821,9 +1837,9 @@
       <c r="H8"/>
       <c r="I8"/>
     </row>
-    <row r="9" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" s="2" customFormat="1">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B9" s="4">
         <f>1410+2189+320+59</f>
@@ -1845,9 +1861,9 @@
       <c r="H9"/>
       <c r="I9"/>
     </row>
-    <row r="10" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" s="2" customFormat="1">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B10" s="4">
         <f>130+126+33+57+173+130</f>
@@ -1869,9 +1885,9 @@
       <c r="H10"/>
       <c r="I10"/>
     </row>
-    <row r="11" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" s="2" customFormat="1">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B11" s="4">
         <f>724+289+144+275-367</f>
@@ -1893,9 +1909,9 @@
       <c r="H11"/>
       <c r="I11"/>
     </row>
-    <row r="12" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" s="2" customFormat="1">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B12" s="4">
         <f>3770+209+935+289</f>
@@ -1917,7 +1933,7 @@
       <c r="H12"/>
       <c r="I12"/>
     </row>
-    <row r="13" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" s="2" customFormat="1">
       <c r="A13" t="s">
         <v>53</v>
       </c>
@@ -1942,9 +1958,9 @@
       <c r="H13"/>
       <c r="I13"/>
     </row>
-    <row r="14" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" s="2" customFormat="1">
       <c r="A14" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B14" s="4">
         <f>((840+420)*2+290+562)+3372</f>
@@ -1966,9 +1982,9 @@
       <c r="H14"/>
       <c r="I14"/>
     </row>
-    <row r="15" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" s="2" customFormat="1">
       <c r="A15" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B15" s="4">
         <f>1280+1280+1280+910+1300+1300+2940+1300-2365+1475-2568-1840</f>
@@ -1991,9 +2007,9 @@
       <c r="I15"/>
       <c r="J15" s="5"/>
     </row>
-    <row r="16" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" s="2" customFormat="1">
       <c r="A16" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B16" s="4">
         <f>(410+205+135+181)*2</f>
@@ -2015,9 +2031,9 @@
       <c r="H16"/>
       <c r="I16"/>
     </row>
-    <row r="17" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" s="2" customFormat="1">
       <c r="A17" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B17" s="4">
         <f>(1875+937+309+619)*2*2-3720-1759-2877-896-2991</f>
@@ -2041,9 +2057,9 @@
       <c r="H17"/>
       <c r="I17"/>
     </row>
-    <row r="18" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" s="2" customFormat="1">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B18" s="4">
         <f>13763+6317+2811+3464+1538</f>
@@ -2065,9 +2081,9 @@
       <c r="H18"/>
       <c r="I18"/>
     </row>
-    <row r="19" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" s="2" customFormat="1">
       <c r="A19" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B19" s="4">
         <f>458+115+189</f>
@@ -2089,9 +2105,9 @@
       <c r="H19"/>
       <c r="I19"/>
     </row>
-    <row r="20" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" s="2" customFormat="1">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B20" s="4">
         <f>(3075+1537+1153-53-1428-925-484-459-467-45+2345+1175)*2</f>
@@ -2113,9 +2129,9 @@
       <c r="H20"/>
       <c r="I20"/>
     </row>
-    <row r="21" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" s="2" customFormat="1">
       <c r="A21" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B21" s="4">
         <f>7985+1084+1117+2249-5230-405-983-767-1715</f>
@@ -2138,9 +2154,9 @@
       </c>
       <c r="H21"/>
     </row>
-    <row r="22" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" s="2" customFormat="1">
       <c r="A22" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B22" s="4">
         <f>2592+518+820</f>
@@ -2162,9 +2178,9 @@
       <c r="H22"/>
       <c r="I22"/>
     </row>
-    <row r="23" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" s="2" customFormat="1">
       <c r="A23" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B23" s="4">
         <f>40235+4295+1952-475+9018-12666-5975-9817+11418+1366-3600+5427-7979-25132+6426+17836-15111-2801-1247-5505-1765+3820-6212+5704-2774+2757-458-1307+3879-7827-231</f>
@@ -2188,7 +2204,7 @@
       <c r="H23"/>
       <c r="I23"/>
     </row>
-    <row r="24" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" s="2" customFormat="1">
       <c r="A24"/>
       <c r="B24" s="4"/>
       <c r="D24"/>
@@ -2198,7 +2214,7 @@
       <c r="H24"/>
       <c r="I24"/>
     </row>
-    <row r="25" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" s="2" customFormat="1">
       <c r="A25"/>
       <c r="B25" s="4"/>
       <c r="D25">
@@ -2223,21 +2239,21 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J26"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2245,15 +2261,15 @@
         <v>46147</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -2270,13 +2286,13 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" s="2" customFormat="1">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="B5" s="4">
         <f>2265+463+942</f>
@@ -2298,9 +2314,9 @@
       <c r="H5"/>
       <c r="I5"/>
     </row>
-    <row r="6" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" s="2" customFormat="1">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B6" s="4">
         <f>4326+2424</f>
@@ -2322,7 +2338,7 @@
       <c r="H6"/>
       <c r="I6"/>
     </row>
-    <row r="7" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" s="2" customFormat="1">
       <c r="A7" t="s">
         <v>47</v>
       </c>
@@ -2345,9 +2361,9 @@
       <c r="H7"/>
       <c r="I7"/>
     </row>
-    <row r="8" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" s="2" customFormat="1">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B8" s="4">
         <f>448*2+37+403+478+149+306+290</f>
@@ -2369,9 +2385,9 @@
       <c r="H8"/>
       <c r="I8"/>
     </row>
-    <row r="9" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" s="2" customFormat="1">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B9" s="4">
         <f>1410+2189+320+59</f>
@@ -2393,9 +2409,9 @@
       <c r="H9"/>
       <c r="I9"/>
     </row>
-    <row r="10" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" s="2" customFormat="1">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B10" s="4">
         <f>130+126+33+57+173+130</f>
@@ -2417,9 +2433,9 @@
       <c r="H10"/>
       <c r="I10"/>
     </row>
-    <row r="11" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" s="2" customFormat="1">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B11" s="4">
         <f>724+289+144+275-367</f>
@@ -2441,9 +2457,9 @@
       <c r="H11"/>
       <c r="I11"/>
     </row>
-    <row r="12" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" s="2" customFormat="1">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B12" s="4">
         <f>3770+209+935+289</f>
@@ -2465,7 +2481,7 @@
       <c r="H12"/>
       <c r="I12"/>
     </row>
-    <row r="13" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" s="2" customFormat="1">
       <c r="A13" t="s">
         <v>53</v>
       </c>
@@ -2488,9 +2504,9 @@
       <c r="H13"/>
       <c r="I13"/>
     </row>
-    <row r="14" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" s="2" customFormat="1">
       <c r="A14" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B14" s="4">
         <f>((840+420)*2+290+562)+3372-130</f>
@@ -2509,14 +2525,14 @@
       </c>
       <c r="F14"/>
       <c r="G14" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H14"/>
       <c r="I14"/>
     </row>
-    <row r="15" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" s="2" customFormat="1">
       <c r="A15" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B15" s="4">
         <f>1280+1280+1280+910+1300+1300+2940+1300-2365+1475-2568-1840</f>
@@ -2539,9 +2555,9 @@
       <c r="I15"/>
       <c r="J15" s="5"/>
     </row>
-    <row r="16" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" s="2" customFormat="1">
       <c r="A16" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B16" s="4">
         <v>12359</v>
@@ -2559,15 +2575,15 @@
       </c>
       <c r="F16"/>
       <c r="G16" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H16"/>
       <c r="I16"/>
       <c r="J16" s="5"/>
     </row>
-    <row r="17" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" s="2" customFormat="1">
       <c r="A17" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B17" s="4">
         <f>(410+205+135+181)*2</f>
@@ -2589,9 +2605,9 @@
       <c r="H17"/>
       <c r="I17"/>
     </row>
-    <row r="18" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" s="2" customFormat="1">
       <c r="A18" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B18" s="4">
         <f>(1875+937+309+619)*2*2-3720-1759-2877-896-2991-2717</f>
@@ -2610,14 +2626,14 @@
       </c>
       <c r="F18"/>
       <c r="G18" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H18"/>
       <c r="I18"/>
     </row>
-    <row r="19" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" s="2" customFormat="1">
       <c r="A19" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B19" s="4">
         <f>13763+6317+2811+3464+1538</f>
@@ -2639,9 +2655,9 @@
       <c r="H19"/>
       <c r="I19"/>
     </row>
-    <row r="20" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" s="2" customFormat="1">
       <c r="A20" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B20" s="4">
         <f>458+115+189</f>
@@ -2663,9 +2679,9 @@
       <c r="H20"/>
       <c r="I20"/>
     </row>
-    <row r="21" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" s="2" customFormat="1">
       <c r="A21" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B21" s="4">
         <f>(3075+1537+1153-53-1428-925-484-459-467-45+2345+1175)*2</f>
@@ -2687,9 +2703,9 @@
       <c r="H21"/>
       <c r="I21"/>
     </row>
-    <row r="22" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" s="2" customFormat="1">
       <c r="A22" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B22" s="4">
         <f>7985+1084+1117+2249-5230-405-983-767-1715-339</f>
@@ -2708,13 +2724,13 @@
       </c>
       <c r="F22"/>
       <c r="G22" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H22"/>
     </row>
-    <row r="23" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" s="2" customFormat="1">
       <c r="A23" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B23" s="4">
         <f>2592+518+820</f>
@@ -2736,9 +2752,9 @@
       <c r="H23"/>
       <c r="I23"/>
     </row>
-    <row r="24" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" s="2" customFormat="1">
       <c r="A24" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B24" s="4">
         <f>40235+4295+1952-475+9018-12666-5975-9817+11418+1366-3600+5427-7979-25132+6426+17836-15111-2801-1247-5505-1765+3820-6212+5704-2774+2757-458-1307+3879-7827-231-3251</f>
@@ -2757,12 +2773,12 @@
       </c>
       <c r="F24"/>
       <c r="G24" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H24"/>
       <c r="I24"/>
     </row>
-    <row r="25" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" s="2" customFormat="1">
       <c r="A25"/>
       <c r="B25" s="4"/>
       <c r="D25"/>
@@ -2772,7 +2788,7 @@
       <c r="H25"/>
       <c r="I25"/>
     </row>
-    <row r="26" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" s="2" customFormat="1">
       <c r="A26"/>
       <c r="B26" s="4"/>
       <c r="D26">
@@ -2797,21 +2813,21 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2819,15 +2835,15 @@
         <v>46147</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -2844,13 +2860,13 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" s="2" customFormat="1">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="B5" s="4">
         <f>2265+463+942</f>
@@ -2872,9 +2888,9 @@
       <c r="H5"/>
       <c r="I5"/>
     </row>
-    <row r="6" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" s="2" customFormat="1">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B6" s="4">
         <f>4326+2424</f>
@@ -2896,7 +2912,7 @@
       <c r="H6"/>
       <c r="I6"/>
     </row>
-    <row r="7" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" s="2" customFormat="1">
       <c r="A7" t="s">
         <v>47</v>
       </c>
@@ -2919,9 +2935,9 @@
       <c r="H7"/>
       <c r="I7"/>
     </row>
-    <row r="8" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" s="2" customFormat="1">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B8" s="4">
         <f>448*2+37+403+478+149+306+290</f>
@@ -2943,9 +2959,9 @@
       <c r="H8"/>
       <c r="I8"/>
     </row>
-    <row r="9" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" s="2" customFormat="1">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B9" s="4">
         <f>1410+2189+320+59</f>
@@ -2967,9 +2983,9 @@
       <c r="H9"/>
       <c r="I9"/>
     </row>
-    <row r="10" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" s="2" customFormat="1">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B10" s="4">
         <f>130+126+33+57+173+130</f>
@@ -2991,9 +3007,9 @@
       <c r="H10"/>
       <c r="I10"/>
     </row>
-    <row r="11" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" s="2" customFormat="1">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B11" s="4">
         <f>724+289+144+275-367</f>
@@ -3015,9 +3031,9 @@
       <c r="H11"/>
       <c r="I11"/>
     </row>
-    <row r="12" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" s="2" customFormat="1">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B12" s="4">
         <f>3770+209+935+289</f>
@@ -3039,7 +3055,7 @@
       <c r="H12"/>
       <c r="I12"/>
     </row>
-    <row r="13" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" s="2" customFormat="1">
       <c r="A13" t="s">
         <v>53</v>
       </c>
@@ -3062,9 +3078,9 @@
       <c r="H13"/>
       <c r="I13"/>
     </row>
-    <row r="14" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" s="2" customFormat="1">
       <c r="A14" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B14" s="4">
         <f>((840+420)*2+290+562)+3372-130-373</f>
@@ -3088,9 +3104,9 @@
       <c r="H14"/>
       <c r="I14"/>
     </row>
-    <row r="15" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" s="2" customFormat="1">
       <c r="A15" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B15" s="4">
         <f>1280+1280+1280+910+1300+1300+2940+1300-2365+1475-2568-1840</f>
@@ -3113,9 +3129,9 @@
       <c r="I15"/>
       <c r="J15" s="5"/>
     </row>
-    <row r="16" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" s="2" customFormat="1">
       <c r="A16" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B16" s="4">
         <f>12359+1297</f>
@@ -3140,9 +3156,9 @@
       <c r="I16"/>
       <c r="J16" s="5"/>
     </row>
-    <row r="17" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" s="2" customFormat="1">
       <c r="A17" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B17" s="4">
         <f>(410+205+135+181)*2</f>
@@ -3164,9 +3180,9 @@
       <c r="H17"/>
       <c r="I17"/>
     </row>
-    <row r="18" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" s="2" customFormat="1">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B18" s="4">
         <f>13763+6317+2811+3464+1538</f>
@@ -3188,9 +3204,9 @@
       <c r="H18"/>
       <c r="I18"/>
     </row>
-    <row r="19" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" s="2" customFormat="1">
       <c r="A19" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B19" s="4">
         <f>458+115+189</f>
@@ -3212,9 +3228,9 @@
       <c r="H19"/>
       <c r="I19"/>
     </row>
-    <row r="20" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" s="2" customFormat="1">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B20" s="4">
         <f>(3075+1537+1153-53-1428-925-484-459-467-45+2345+1175)*2</f>
@@ -3236,9 +3252,9 @@
       <c r="H20"/>
       <c r="I20"/>
     </row>
-    <row r="21" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" s="2" customFormat="1">
       <c r="A21" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B21" s="4">
         <f>7985+1084+1117+2249-5230-405-983-767-1715-339</f>
@@ -3259,9 +3275,9 @@
       <c r="G21"/>
       <c r="H21"/>
     </row>
-    <row r="22" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" s="2" customFormat="1">
       <c r="A22" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B22" s="4">
         <f>2592+518+820</f>
@@ -3283,9 +3299,9 @@
       <c r="H22"/>
       <c r="I22"/>
     </row>
-    <row r="23" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" s="2" customFormat="1">
       <c r="A23" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B23" s="4">
         <f>40235+4295+1952-475+9018-12666-5975-9817+11418+1366-3600+5427-7979-25132+6426+17836-15111-2801-1247-5505-1765+3820-6212+5704-2774+2757-458-1307+3879-7827-231-3251</f>
@@ -3307,7 +3323,7 @@
       <c r="H23"/>
       <c r="I23"/>
     </row>
-    <row r="24" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" s="2" customFormat="1">
       <c r="A24"/>
       <c r="B24" s="4"/>
       <c r="D24"/>
@@ -3317,7 +3333,7 @@
       <c r="H24"/>
       <c r="I24"/>
     </row>
-    <row r="25" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" s="2" customFormat="1">
       <c r="A25"/>
       <c r="B25" s="4"/>
       <c r="D25">
@@ -3342,21 +3358,21 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3368,11 +3384,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -3389,13 +3405,13 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" s="2" customFormat="1">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="B5" s="4">
         <f>2265+463+942</f>
@@ -3417,9 +3433,9 @@
       <c r="H5"/>
       <c r="I5"/>
     </row>
-    <row r="6" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" s="2" customFormat="1">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B6" s="4">
         <f>4326+2424</f>
@@ -3441,7 +3457,7 @@
       <c r="H6"/>
       <c r="I6"/>
     </row>
-    <row r="7" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" s="2" customFormat="1">
       <c r="A7" t="s">
         <v>47</v>
       </c>
@@ -3464,9 +3480,9 @@
       <c r="H7"/>
       <c r="I7"/>
     </row>
-    <row r="8" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" s="2" customFormat="1">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B8" s="4">
         <f>448*2+37+403+478+149+306+290</f>
@@ -3488,9 +3504,9 @@
       <c r="H8"/>
       <c r="I8"/>
     </row>
-    <row r="9" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" s="2" customFormat="1">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B9" s="4">
         <f>1410+2189+320+59</f>
@@ -3512,9 +3528,9 @@
       <c r="H9"/>
       <c r="I9"/>
     </row>
-    <row r="10" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" s="2" customFormat="1">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B10" s="4">
         <f>130+126+33+57+173+130</f>
@@ -3536,9 +3552,9 @@
       <c r="H10"/>
       <c r="I10"/>
     </row>
-    <row r="11" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" s="2" customFormat="1">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B11" s="4">
         <f>(724+289+144+275-367)*10</f>
@@ -3562,9 +3578,9 @@
       <c r="H11"/>
       <c r="I11"/>
     </row>
-    <row r="12" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" s="2" customFormat="1">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B12" s="4">
         <f>3770+209+935+289</f>
@@ -3586,7 +3602,7 @@
       <c r="H12"/>
       <c r="I12"/>
     </row>
-    <row r="13" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" s="2" customFormat="1">
       <c r="A13" t="s">
         <v>53</v>
       </c>
@@ -3609,9 +3625,9 @@
       <c r="H13"/>
       <c r="I13"/>
     </row>
-    <row r="14" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" s="2" customFormat="1">
       <c r="A14" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B14" s="4">
         <f>((840+420)*2+290+562)+3372-130-373</f>
@@ -3633,9 +3649,9 @@
       <c r="H14"/>
       <c r="I14"/>
     </row>
-    <row r="15" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" s="2" customFormat="1">
       <c r="A15" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B15" s="4">
         <f>1280+1280+1280+910+1300+1300+2940+1300-2365+1475-2568-1840</f>
@@ -3658,9 +3674,9 @@
       <c r="I15"/>
       <c r="J15" s="5"/>
     </row>
-    <row r="16" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" s="2" customFormat="1">
       <c r="A16" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B16" s="4">
         <f>12359+1297</f>
@@ -3683,9 +3699,9 @@
       <c r="I16"/>
       <c r="J16" s="5"/>
     </row>
-    <row r="17" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" s="2" customFormat="1">
       <c r="A17" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B17" s="4">
         <f>(410+205+135+181)*2</f>
@@ -3707,9 +3723,9 @@
       <c r="H17"/>
       <c r="I17"/>
     </row>
-    <row r="18" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" s="2" customFormat="1">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B18" s="4">
         <f>13763+6317+2811+3464+1538</f>
@@ -3731,9 +3747,9 @@
       <c r="H18"/>
       <c r="I18"/>
     </row>
-    <row r="19" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" s="2" customFormat="1">
       <c r="A19" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B19" s="4">
         <f>458+115+189</f>
@@ -3755,9 +3771,9 @@
       <c r="H19"/>
       <c r="I19"/>
     </row>
-    <row r="20" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" s="2" customFormat="1">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B20" s="4">
         <f>(3075+1537+1153-53-1428-925-484-459-467-45+2345+1175)*2</f>
@@ -3779,9 +3795,9 @@
       <c r="H20"/>
       <c r="I20"/>
     </row>
-    <row r="21" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" s="2" customFormat="1">
       <c r="A21" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B21" s="4">
         <f>7985+1084+1117+2249-5230-405-983-767-1715-339</f>
@@ -3802,9 +3818,9 @@
       <c r="G21"/>
       <c r="H21"/>
     </row>
-    <row r="22" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" s="2" customFormat="1">
       <c r="A22" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B22" s="4">
         <f>2592+518+820</f>
@@ -3826,9 +3842,9 @@
       <c r="H22"/>
       <c r="I22"/>
     </row>
-    <row r="23" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" s="2" customFormat="1">
       <c r="A23" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B23" s="4">
         <f>40235+4295+1952-475+9018-12666-5975-9817+11418+1366-3600+5427-7979-25132+6426+17836-15111-2801-1247-5505-1765+3820-6212+5704-2774+2757-458-1307+3879-7827-231-3251</f>
@@ -3850,7 +3866,7 @@
       <c r="H23"/>
       <c r="I23"/>
     </row>
-    <row r="24" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" s="2" customFormat="1">
       <c r="A24"/>
       <c r="B24" s="4"/>
       <c r="D24"/>
@@ -3860,7 +3876,7 @@
       <c r="H24"/>
       <c r="I24"/>
     </row>
-    <row r="25" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" s="2" customFormat="1">
       <c r="A25"/>
       <c r="B25" s="4"/>
       <c r="D25">
@@ -3885,21 +3901,21 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3911,11 +3927,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -3932,13 +3948,13 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" s="2" customFormat="1">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="B5" s="4">
         <f>2265+463+942</f>
@@ -3960,9 +3976,9 @@
       <c r="H5"/>
       <c r="I5"/>
     </row>
-    <row r="6" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" s="2" customFormat="1">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B6" s="4">
         <f>4326+2424</f>
@@ -3984,7 +4000,7 @@
       <c r="H6"/>
       <c r="I6"/>
     </row>
-    <row r="7" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" s="2" customFormat="1">
       <c r="A7" t="s">
         <v>47</v>
       </c>
@@ -4007,9 +4023,9 @@
       <c r="H7"/>
       <c r="I7"/>
     </row>
-    <row r="8" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" s="2" customFormat="1">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B8" s="4">
         <f>448*2+37+403+478+149+306+290</f>
@@ -4031,9 +4047,9 @@
       <c r="H8"/>
       <c r="I8"/>
     </row>
-    <row r="9" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" s="2" customFormat="1">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B9" s="4">
         <f>1410+2189+320+59</f>
@@ -4055,9 +4071,9 @@
       <c r="H9"/>
       <c r="I9"/>
     </row>
-    <row r="10" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" s="2" customFormat="1">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B10" s="4">
         <f>130+126+33+57+173+130</f>
@@ -4079,9 +4095,9 @@
       <c r="H10"/>
       <c r="I10"/>
     </row>
-    <row r="11" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" s="2" customFormat="1">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B11" s="4">
         <f>(724+289+144+275-367)*10</f>
@@ -4103,9 +4119,9 @@
       <c r="H11"/>
       <c r="I11"/>
     </row>
-    <row r="12" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" s="2" customFormat="1">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B12" s="4">
         <f>3770+209+935+289</f>
@@ -4127,7 +4143,7 @@
       <c r="H12"/>
       <c r="I12"/>
     </row>
-    <row r="13" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" s="2" customFormat="1">
       <c r="A13" t="s">
         <v>53</v>
       </c>
@@ -4148,14 +4164,14 @@
       </c>
       <c r="F13"/>
       <c r="G13" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H13"/>
       <c r="I13"/>
     </row>
-    <row r="14" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" s="2" customFormat="1">
       <c r="A14" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B14" s="4">
         <f>((840+420)*2+290+562)+3372-130-373</f>
@@ -4177,9 +4193,9 @@
       <c r="H14"/>
       <c r="I14"/>
     </row>
-    <row r="15" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" s="2" customFormat="1">
       <c r="A15" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B15" s="4">
         <f>1280+1280+1280+910+1300+1300+2940+1300-2365+1475-2568-1840-1507</f>
@@ -4198,15 +4214,15 @@
       </c>
       <c r="F15"/>
       <c r="G15" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H15"/>
       <c r="I15"/>
       <c r="J15" s="5"/>
     </row>
-    <row r="16" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" s="2" customFormat="1">
       <c r="A16" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B16" s="4">
         <f>12359+1297</f>
@@ -4229,9 +4245,9 @@
       <c r="I16"/>
       <c r="J16" s="5"/>
     </row>
-    <row r="17" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" s="2" customFormat="1">
       <c r="A17" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B17" s="4">
         <f>(410+205+135+181)*2</f>
@@ -4253,9 +4269,9 @@
       <c r="H17"/>
       <c r="I17"/>
     </row>
-    <row r="18" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" s="2" customFormat="1">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B18" s="4">
         <f>13763+6317+2811+3464+1538</f>
@@ -4277,9 +4293,9 @@
       <c r="H18"/>
       <c r="I18"/>
     </row>
-    <row r="19" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" s="2" customFormat="1">
       <c r="A19" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B19" s="4">
         <f>458+115+189</f>
@@ -4301,9 +4317,9 @@
       <c r="H19"/>
       <c r="I19"/>
     </row>
-    <row r="20" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" s="2" customFormat="1">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B20" s="4">
         <f>(3075+1537+1153-53-1428-925-484-459-467-45+2345+1175)*2</f>
@@ -4325,9 +4341,9 @@
       <c r="H20"/>
       <c r="I20"/>
     </row>
-    <row r="21" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" s="2" customFormat="1">
       <c r="A21" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B21" s="4">
         <f>7985+1084+1117+2249-5230-405-983-767-1715-339</f>
@@ -4348,9 +4364,9 @@
       <c r="G21"/>
       <c r="H21"/>
     </row>
-    <row r="22" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" s="2" customFormat="1">
       <c r="A22" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B22" s="4">
         <f>2592+518+820</f>
@@ -4372,9 +4388,9 @@
       <c r="H22"/>
       <c r="I22"/>
     </row>
-    <row r="23" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" s="2" customFormat="1">
       <c r="A23" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B23" s="4">
         <f>40235+4295+1952-475+9018-12666-5975-9817+11418+1366-3600+5427-7979-25132+6426+17836-15111-2801-1247-5505-1765+3820-6212+5704-2774+2757-458-1307+3879-7827-231-3251</f>
@@ -4396,7 +4412,7 @@
       <c r="H23"/>
       <c r="I23"/>
     </row>
-    <row r="24" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" s="2" customFormat="1">
       <c r="A24"/>
       <c r="B24" s="4"/>
       <c r="D24"/>
@@ -4406,7 +4422,7 @@
       <c r="H24"/>
       <c r="I24"/>
     </row>
-    <row r="25" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" s="2" customFormat="1">
       <c r="A25"/>
       <c r="B25" s="4"/>
       <c r="D25">
@@ -4431,21 +4447,21 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4457,11 +4473,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -4478,13 +4494,13 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" s="2" customFormat="1">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="B5" s="4">
         <f>2265+463+942</f>
@@ -4506,9 +4522,9 @@
       <c r="H5"/>
       <c r="I5"/>
     </row>
-    <row r="6" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" s="2" customFormat="1">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B6" s="4">
         <f>4326+2424</f>
@@ -4530,7 +4546,7 @@
       <c r="H6"/>
       <c r="I6"/>
     </row>
-    <row r="7" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" s="2" customFormat="1">
       <c r="A7" t="s">
         <v>47</v>
       </c>
@@ -4551,14 +4567,14 @@
       </c>
       <c r="F7"/>
       <c r="G7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H7"/>
       <c r="I7"/>
     </row>
-    <row r="8" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" s="2" customFormat="1">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B8" s="4">
         <f>448*2+37+403+478+149+306+290</f>
@@ -4580,9 +4596,9 @@
       <c r="H8"/>
       <c r="I8"/>
     </row>
-    <row r="9" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" s="2" customFormat="1">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B9" s="4">
         <f>1410+2189+320+59</f>
@@ -4604,9 +4620,9 @@
       <c r="H9"/>
       <c r="I9"/>
     </row>
-    <row r="10" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" s="2" customFormat="1">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B10" s="4">
         <f>130+126+33+57+173+130</f>
@@ -4628,9 +4644,9 @@
       <c r="H10"/>
       <c r="I10"/>
     </row>
-    <row r="11" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" s="2" customFormat="1">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B11" s="4">
         <f>(724+289+144+275-367)*10-3094</f>
@@ -4654,9 +4670,9 @@
       <c r="H11"/>
       <c r="I11"/>
     </row>
-    <row r="12" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" s="2" customFormat="1">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B12" s="4">
         <f>3770+209+935+289</f>
@@ -4678,7 +4694,7 @@
       <c r="H12"/>
       <c r="I12"/>
     </row>
-    <row r="13" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" s="2" customFormat="1">
       <c r="A13" t="s">
         <v>53</v>
       </c>
@@ -4702,9 +4718,9 @@
       <c r="H13"/>
       <c r="I13"/>
     </row>
-    <row r="14" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" s="2" customFormat="1">
       <c r="A14" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B14" s="4">
         <f>((840+420)*2+290+562)+3372-130-373</f>
@@ -4726,9 +4742,9 @@
       <c r="H14"/>
       <c r="I14"/>
     </row>
-    <row r="15" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" s="2" customFormat="1">
       <c r="A15" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B15" s="4">
         <f>1280+1280+1280+910+1300+1300+2940+1300-2365+1475-2568-1840-1507</f>
@@ -4751,9 +4767,9 @@
       <c r="I15"/>
       <c r="J15" s="5"/>
     </row>
-    <row r="16" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" s="2" customFormat="1">
       <c r="A16" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B16" s="4">
         <f>12359+1297</f>
@@ -4776,9 +4792,9 @@
       <c r="I16"/>
       <c r="J16" s="5"/>
     </row>
-    <row r="17" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" s="2" customFormat="1">
       <c r="A17" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B17" s="4">
         <f>(410+205+135+181)*2-143</f>
@@ -4797,14 +4813,14 @@
       </c>
       <c r="F17"/>
       <c r="G17" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H17"/>
       <c r="I17"/>
     </row>
-    <row r="18" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" s="2" customFormat="1">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B18" s="4">
         <f>13763+6317+2811+3464+1538</f>
@@ -4826,9 +4842,9 @@
       <c r="H18"/>
       <c r="I18"/>
     </row>
-    <row r="19" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" s="2" customFormat="1">
       <c r="A19" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B19" s="4">
         <f>458+115+189</f>
@@ -4850,9 +4866,9 @@
       <c r="H19"/>
       <c r="I19"/>
     </row>
-    <row r="20" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" s="2" customFormat="1">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B20" s="4">
         <f>(3075+1537+1153-53-1428-925-484-459-467-45+2345+1175)*2</f>
@@ -4874,9 +4890,9 @@
       <c r="H20"/>
       <c r="I20"/>
     </row>
-    <row r="21" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" s="2" customFormat="1">
       <c r="A21" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B21" s="4">
         <f>7985+1084+1117+2249-5230-405-983-767-1715-339-205</f>
@@ -4899,9 +4915,9 @@
       </c>
       <c r="H21"/>
     </row>
-    <row r="22" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" s="2" customFormat="1">
       <c r="A22" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B22" s="4">
         <f>2592+518+820</f>
@@ -4923,9 +4939,9 @@
       <c r="H22"/>
       <c r="I22"/>
     </row>
-    <row r="23" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" s="2" customFormat="1">
       <c r="A23" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B23" s="4">
         <f>40235+4295+1952-475+9018-12666-5975-9817+11418+1366-3600+5427-7979-25132+6426+17836-15111-2801-1247-5505-1765+3820-6212+5704-2774+2757-458-1307+3879-7827-231-3251+13804</f>
@@ -4949,7 +4965,7 @@
       <c r="H23"/>
       <c r="I23"/>
     </row>
-    <row r="24" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" s="2" customFormat="1">
       <c r="A24"/>
       <c r="B24" s="4"/>
       <c r="D24"/>
@@ -4959,7 +4975,7 @@
       <c r="H24"/>
       <c r="I24"/>
     </row>
-    <row r="25" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" s="2" customFormat="1">
       <c r="A25"/>
       <c r="B25" s="4"/>
       <c r="D25">
@@ -4984,21 +5000,21 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5006,15 +5022,15 @@
         <v>46182</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -5031,13 +5047,13 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" s="2" customFormat="1">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="B5" s="4">
         <f>2265+463+942</f>
@@ -5059,9 +5075,9 @@
       <c r="H5"/>
       <c r="I5"/>
     </row>
-    <row r="6" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" s="2" customFormat="1">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B6" s="4">
         <f>4326+2424</f>
@@ -5083,7 +5099,7 @@
       <c r="H6"/>
       <c r="I6"/>
     </row>
-    <row r="7" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" s="2" customFormat="1">
       <c r="A7" t="s">
         <v>47</v>
       </c>
@@ -5107,9 +5123,9 @@
       <c r="H7"/>
       <c r="I7"/>
     </row>
-    <row r="8" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" s="2" customFormat="1">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B8" s="4">
         <f>448*2+37+403+478+149+306+290</f>
@@ -5131,9 +5147,9 @@
       <c r="H8"/>
       <c r="I8"/>
     </row>
-    <row r="9" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" s="2" customFormat="1">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B9" s="4">
         <f>1410+2189+320+59</f>
@@ -5155,9 +5171,9 @@
       <c r="H9"/>
       <c r="I9"/>
     </row>
-    <row r="10" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" s="2" customFormat="1">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B10" s="4">
         <f>130+126+33+57+173+130</f>
@@ -5179,9 +5195,9 @@
       <c r="H10"/>
       <c r="I10"/>
     </row>
-    <row r="11" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" s="2" customFormat="1">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B11" s="4">
         <f>(724+289+144+275-367)*10-3094</f>
@@ -5203,9 +5219,9 @@
       <c r="H11"/>
       <c r="I11"/>
     </row>
-    <row r="12" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" s="2" customFormat="1">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B12" s="4">
         <f>3770+209+935+289</f>
@@ -5227,7 +5243,7 @@
       <c r="H12"/>
       <c r="I12"/>
     </row>
-    <row r="13" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" s="2" customFormat="1">
       <c r="A13" t="s">
         <v>53</v>
       </c>
@@ -5251,9 +5267,9 @@
       <c r="H13"/>
       <c r="I13"/>
     </row>
-    <row r="14" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" s="2" customFormat="1">
       <c r="A14" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B14" s="4">
         <f>((840+420)*2+290+562)+3372-130-373</f>
@@ -5275,9 +5291,9 @@
       <c r="H14"/>
       <c r="I14"/>
     </row>
-    <row r="15" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" s="2" customFormat="1">
       <c r="A15" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B15" s="4">
         <f>1280+1280+1280+910+1300+1300+2940+1300-2365+1475-2568-1840-1507</f>
@@ -5300,9 +5316,9 @@
       <c r="I15"/>
       <c r="J15" s="5"/>
     </row>
-    <row r="16" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" s="2" customFormat="1">
       <c r="A16" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B16" s="4">
         <f>12359+1297</f>
@@ -5325,9 +5341,9 @@
       <c r="I16"/>
       <c r="J16" s="5"/>
     </row>
-    <row r="17" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" s="2" customFormat="1">
       <c r="A17" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B17" s="4">
         <f>(410+205+135+181)*2-143</f>
@@ -5349,9 +5365,9 @@
       <c r="H17"/>
       <c r="I17"/>
     </row>
-    <row r="18" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" s="2" customFormat="1">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B18" s="4">
         <f>13763+6317+2811+3464+1538</f>
@@ -5373,9 +5389,9 @@
       <c r="H18"/>
       <c r="I18"/>
     </row>
-    <row r="19" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" s="2" customFormat="1">
       <c r="A19" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B19" s="4">
         <f>458+115+189</f>
@@ -5397,9 +5413,9 @@
       <c r="H19"/>
       <c r="I19"/>
     </row>
-    <row r="20" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" s="2" customFormat="1">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B20" s="4">
         <f>(3075+1537+1153-53-1428-925-484-459-467-45+2345+1175)*2</f>
@@ -5421,9 +5437,9 @@
       <c r="H20"/>
       <c r="I20"/>
     </row>
-    <row r="21" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" s="2" customFormat="1">
       <c r="A21" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B21" s="4">
         <f>7985+1084+1117+2249-5230-405-983-767-1715-339-205-937</f>
@@ -5442,13 +5458,13 @@
       </c>
       <c r="F21"/>
       <c r="G21" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H21"/>
     </row>
-    <row r="22" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" s="2" customFormat="1">
       <c r="A22" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B22" s="4">
         <f>2592+518+820</f>
@@ -5470,9 +5486,9 @@
       <c r="H22"/>
       <c r="I22"/>
     </row>
-    <row r="23" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" s="2" customFormat="1">
       <c r="A23" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B23" s="4">
         <f>40235+4295+1952-475+9018-12666-5975-9817+11418+1366-3600+5427-7979-25132+6426+17836-15111-2801-1247-5505-1765+3820-6212+5704-2774+2757-458-1307+3879-7827-231-3251+13804+4918</f>
@@ -5496,7 +5512,7 @@
       <c r="H23"/>
       <c r="I23"/>
     </row>
-    <row r="24" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" s="2" customFormat="1">
       <c r="A24"/>
       <c r="B24" s="4"/>
       <c r="D24"/>
@@ -5506,7 +5522,7 @@
       <c r="H24"/>
       <c r="I24"/>
     </row>
-    <row r="25" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" s="2" customFormat="1">
       <c r="A25"/>
       <c r="B25" s="4"/>
       <c r="D25">
@@ -5526,11 +5542,1096 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E270A1E4-8160-48C8-BABC-214DD704FB6A}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B71E0724-5CD2-4776-891C-F7CEA8D1BBE8}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J25"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
+  <cols>
+    <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="2"/>
+    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11" customWidth="1"/>
+    <col min="7" max="7" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>46227</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E1" s="3"/>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="B2" s="4"/>
+      <c r="E2" s="3"/>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="B4" s="4"/>
+      <c r="E4" s="3"/>
+    </row>
+    <row r="5" spans="1:10" s="2" customFormat="1">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="4">
+        <f>2265+463+942</f>
+        <v>3670</v>
+      </c>
+      <c r="C5" s="2">
+        <v>686.95</v>
+      </c>
+      <c r="D5">
+        <f t="shared" ref="D5:D23" si="0">C5*B5</f>
+        <v>2521106.5</v>
+      </c>
+      <c r="E5" s="3">
+        <f t="shared" ref="E5:E23" si="1">D5/$D$25</f>
+        <v>3.8715379477151882E-2</v>
+      </c>
+      <c r="F5"/>
+      <c r="G5"/>
+      <c r="H5"/>
+      <c r="I5"/>
+    </row>
+    <row r="6" spans="1:10" s="2" customFormat="1">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="4">
+        <f>4326+2424</f>
+        <v>6750</v>
+      </c>
+      <c r="C6" s="2">
+        <v>1783.1</v>
+      </c>
+      <c r="D6">
+        <f t="shared" si="0"/>
+        <v>12035925</v>
+      </c>
+      <c r="E6" s="3">
+        <f t="shared" si="1"/>
+        <v>0.18482971811525584</v>
+      </c>
+      <c r="F6"/>
+      <c r="G6"/>
+      <c r="H6"/>
+      <c r="I6"/>
+    </row>
+    <row r="7" spans="1:10" s="2" customFormat="1">
+      <c r="A7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="4">
+        <f>1655+330</f>
+        <v>1985</v>
+      </c>
+      <c r="C7" s="2">
+        <v>1233.2</v>
+      </c>
+      <c r="D7">
+        <f t="shared" si="0"/>
+        <v>2447902</v>
+      </c>
+      <c r="E7" s="3">
+        <f t="shared" si="1"/>
+        <v>3.7591214354839447E-2</v>
+      </c>
+      <c r="F7"/>
+      <c r="G7"/>
+      <c r="H7"/>
+      <c r="I7"/>
+    </row>
+    <row r="8" spans="1:10" s="2" customFormat="1">
+      <c r="A8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="4">
+        <f>448*2+37+403+478+149+306+290</f>
+        <v>2559</v>
+      </c>
+      <c r="C8" s="2">
+        <v>808.45</v>
+      </c>
+      <c r="D8">
+        <f t="shared" si="0"/>
+        <v>2068823.55</v>
+      </c>
+      <c r="E8" s="3">
+        <f t="shared" si="1"/>
+        <v>3.1769895008211077E-2</v>
+      </c>
+      <c r="F8"/>
+      <c r="G8"/>
+      <c r="H8"/>
+      <c r="I8"/>
+    </row>
+    <row r="9" spans="1:10" s="2" customFormat="1">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="4">
+        <f>1410+2189+320+59</f>
+        <v>3978</v>
+      </c>
+      <c r="C9" s="2">
+        <v>1740.8</v>
+      </c>
+      <c r="D9">
+        <f t="shared" si="0"/>
+        <v>6924902.3999999994</v>
+      </c>
+      <c r="E9" s="3">
+        <f t="shared" si="1"/>
+        <v>0.10634228433358121</v>
+      </c>
+      <c r="F9"/>
+      <c r="G9"/>
+      <c r="H9"/>
+      <c r="I9"/>
+    </row>
+    <row r="10" spans="1:10" s="2" customFormat="1">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="4">
+        <f>130+126+33+57+173+130</f>
+        <v>649</v>
+      </c>
+      <c r="C10" s="2">
+        <v>1347</v>
+      </c>
+      <c r="D10">
+        <f t="shared" si="0"/>
+        <v>874203</v>
+      </c>
+      <c r="E10" s="3">
+        <f t="shared" si="1"/>
+        <v>1.3424700973586242E-2</v>
+      </c>
+      <c r="F10"/>
+      <c r="G10"/>
+      <c r="H10"/>
+      <c r="I10"/>
+    </row>
+    <row r="11" spans="1:10" s="2" customFormat="1">
+      <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="4">
+        <f>(724+289+144+275-367)*10-3094</f>
+        <v>7556</v>
+      </c>
+      <c r="C11" s="2">
+        <v>492.1</v>
+      </c>
+      <c r="D11">
+        <f t="shared" si="0"/>
+        <v>3718307.6</v>
+      </c>
+      <c r="E11" s="3">
+        <f t="shared" si="1"/>
+        <v>5.7100201735538689E-2</v>
+      </c>
+      <c r="F11"/>
+      <c r="G11"/>
+      <c r="H11"/>
+      <c r="I11"/>
+    </row>
+    <row r="12" spans="1:10" s="2" customFormat="1">
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="4">
+        <f>3770+209+935+289</f>
+        <v>5203</v>
+      </c>
+      <c r="C12" s="2">
+        <v>669.9</v>
+      </c>
+      <c r="D12">
+        <f t="shared" si="0"/>
+        <v>3485489.6999999997</v>
+      </c>
+      <c r="E12" s="3">
+        <f t="shared" si="1"/>
+        <v>5.3524932960667966E-2</v>
+      </c>
+      <c r="F12"/>
+      <c r="G12"/>
+      <c r="H12"/>
+      <c r="I12"/>
+    </row>
+    <row r="13" spans="1:10" s="2" customFormat="1">
+      <c r="A13" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" s="4">
+        <f>2434+532+562</f>
+        <v>3528</v>
+      </c>
+      <c r="C13" s="2">
+        <v>623.85</v>
+      </c>
+      <c r="D13">
+        <f t="shared" si="0"/>
+        <v>2200942.8000000003</v>
+      </c>
+      <c r="E13" s="3">
+        <f t="shared" si="1"/>
+        <v>3.3798784664394468E-2</v>
+      </c>
+      <c r="F13"/>
+      <c r="G13" t="s">
+        <v>80</v>
+      </c>
+      <c r="H13"/>
+      <c r="I13"/>
+    </row>
+    <row r="14" spans="1:10" s="2" customFormat="1">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="4">
+        <f>((840+420)*2+290+562)+3372-130-373</f>
+        <v>6241</v>
+      </c>
+      <c r="C14" s="2">
+        <v>330.05</v>
+      </c>
+      <c r="D14">
+        <f t="shared" si="0"/>
+        <v>2059842.05</v>
+      </c>
+      <c r="E14" s="3">
+        <f t="shared" si="1"/>
+        <v>3.1631970576706879E-2</v>
+      </c>
+      <c r="F14"/>
+      <c r="G14"/>
+      <c r="H14"/>
+      <c r="I14"/>
+    </row>
+    <row r="15" spans="1:10" s="2" customFormat="1">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="4">
+        <f>1280+1280+1280+910+1300+1300+2940+1300-2365+1475-2568-1840-1507</f>
+        <v>4785</v>
+      </c>
+      <c r="C15" s="2">
+        <v>167.5</v>
+      </c>
+      <c r="D15">
+        <f t="shared" si="0"/>
+        <v>801487.5</v>
+      </c>
+      <c r="E15" s="3">
+        <f t="shared" si="1"/>
+        <v>1.2308045181230451E-2</v>
+      </c>
+      <c r="F15"/>
+      <c r="G15"/>
+      <c r="H15"/>
+      <c r="I15"/>
+      <c r="J15" s="5"/>
+    </row>
+    <row r="16" spans="1:10" s="2" customFormat="1">
+      <c r="A16" t="s">
+        <v>60</v>
+      </c>
+      <c r="B16" s="4">
+        <f>12359+1297</f>
+        <v>13656</v>
+      </c>
+      <c r="C16" s="2">
+        <v>76.209999999999994</v>
+      </c>
+      <c r="D16">
+        <f t="shared" si="0"/>
+        <v>1040723.7599999999</v>
+      </c>
+      <c r="E16" s="3">
+        <f t="shared" si="1"/>
+        <v>1.5981877520560253E-2</v>
+      </c>
+      <c r="F16"/>
+      <c r="G16"/>
+      <c r="H16"/>
+      <c r="I16"/>
+      <c r="J16" s="5"/>
+    </row>
+    <row r="17" spans="1:9" s="2" customFormat="1">
+      <c r="A17" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="4">
+        <f>(410+205+135+181)*2-143</f>
+        <v>1719</v>
+      </c>
+      <c r="C17" s="2">
+        <v>2555.6</v>
+      </c>
+      <c r="D17">
+        <f t="shared" si="0"/>
+        <v>4393076.3999999994</v>
+      </c>
+      <c r="E17" s="3">
+        <f t="shared" si="1"/>
+        <v>6.7462290822747961E-2</v>
+      </c>
+      <c r="F17"/>
+      <c r="G17"/>
+      <c r="H17"/>
+      <c r="I17"/>
+    </row>
+    <row r="18" spans="1:9" s="2" customFormat="1">
+      <c r="A18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" s="4">
+        <f>13763+6317+2811+3464+1538</f>
+        <v>27893</v>
+      </c>
+      <c r="C18" s="2">
+        <v>100.29</v>
+      </c>
+      <c r="D18">
+        <f t="shared" si="0"/>
+        <v>2797388.97</v>
+      </c>
+      <c r="E18" s="3">
+        <f t="shared" si="1"/>
+        <v>4.2958112050700374E-2</v>
+      </c>
+      <c r="F18"/>
+      <c r="G18"/>
+      <c r="H18"/>
+      <c r="I18"/>
+    </row>
+    <row r="19" spans="1:9" s="2" customFormat="1">
+      <c r="A19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" s="4">
+        <f>458+115+189</f>
+        <v>762</v>
+      </c>
+      <c r="C19" s="2">
+        <v>6749.5</v>
+      </c>
+      <c r="D19">
+        <f t="shared" si="0"/>
+        <v>5143119</v>
+      </c>
+      <c r="E19" s="3">
+        <f t="shared" si="1"/>
+        <v>7.8980322243883752E-2</v>
+      </c>
+      <c r="F19"/>
+      <c r="G19"/>
+      <c r="H19"/>
+      <c r="I19"/>
+    </row>
+    <row r="20" spans="1:9" s="2" customFormat="1">
+      <c r="A20" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" s="4">
+        <f>(3075+1537+1153-53-1428-925-484-459-467-45+2345+1175)*2</f>
+        <v>10848</v>
+      </c>
+      <c r="C20" s="2">
+        <v>241.4</v>
+      </c>
+      <c r="D20">
+        <f t="shared" si="0"/>
+        <v>2618707.2000000002</v>
+      </c>
+      <c r="E20" s="3">
+        <f t="shared" si="1"/>
+        <v>4.0214184917436002E-2</v>
+      </c>
+      <c r="F20"/>
+      <c r="G20"/>
+      <c r="H20"/>
+      <c r="I20"/>
+    </row>
+    <row r="21" spans="1:9" s="2" customFormat="1">
+      <c r="A21" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" s="4">
+        <f>7985+1084+1117+2249-5230-405-983-767-1715-339-205-937</f>
+        <v>1854</v>
+      </c>
+      <c r="C21" s="2">
+        <v>602</v>
+      </c>
+      <c r="D21">
+        <f t="shared" si="0"/>
+        <v>1116108</v>
+      </c>
+      <c r="E21" s="3">
+        <f t="shared" si="1"/>
+        <v>1.7139515826675718E-2</v>
+      </c>
+      <c r="F21"/>
+      <c r="G21"/>
+      <c r="H21"/>
+    </row>
+    <row r="22" spans="1:9" s="2" customFormat="1">
+      <c r="A22" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" s="4">
+        <f>2592+518+820</f>
+        <v>3930</v>
+      </c>
+      <c r="C22" s="2">
+        <v>1800.7</v>
+      </c>
+      <c r="D22">
+        <f t="shared" si="0"/>
+        <v>7076751</v>
+      </c>
+      <c r="E22" s="3">
+        <f t="shared" si="1"/>
+        <v>0.10867414781180963</v>
+      </c>
+      <c r="F22"/>
+      <c r="G22"/>
+      <c r="H22"/>
+      <c r="I22"/>
+    </row>
+    <row r="23" spans="1:9" s="2" customFormat="1">
+      <c r="A23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" s="4">
+        <f>40235+4295+1952-475+9018-12666-5975-9817+11418+1366-3600+5427-7979-25132+6426+17836-15111-2801-1247-5505-1765+3820-6212+5704-2774+2757-458-1307+3879-7827-231-3251+13804+4918-3138</f>
+        <v>15584</v>
+      </c>
+      <c r="C23" s="2">
+        <v>115.13</v>
+      </c>
+      <c r="D23">
+        <f t="shared" si="0"/>
+        <v>1794185.92</v>
+      </c>
+      <c r="E23" s="3">
+        <f t="shared" si="1"/>
+        <v>2.7552421425022251E-2</v>
+      </c>
+      <c r="F23"/>
+      <c r="G23" t="s">
+        <v>81</v>
+      </c>
+      <c r="H23"/>
+      <c r="I23"/>
+    </row>
+    <row r="24" spans="1:9" s="2" customFormat="1">
+      <c r="A24"/>
+      <c r="B24" s="4"/>
+      <c r="D24"/>
+      <c r="E24" s="3"/>
+      <c r="F24"/>
+      <c r="G24"/>
+      <c r="H24"/>
+      <c r="I24"/>
+    </row>
+    <row r="25" spans="1:9" s="2" customFormat="1">
+      <c r="A25"/>
+      <c r="B25" s="4"/>
+      <c r="D25">
+        <f>SUM(D5:D23)</f>
+        <v>65118992.349999994</v>
+      </c>
+      <c r="E25"/>
+      <c r="F25"/>
+      <c r="G25"/>
+      <c r="H25"/>
+      <c r="I25"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup scale="77" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{674A65A1-4147-4196-BA0F-14F5459B1221}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J25"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
+  <cols>
+    <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="2"/>
+    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11" customWidth="1"/>
+    <col min="7" max="7" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>46231</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E1" s="3"/>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="B2" s="4"/>
+      <c r="E2" s="3"/>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="B4" s="4"/>
+      <c r="E4" s="3"/>
+    </row>
+    <row r="5" spans="1:10" s="2" customFormat="1">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="4">
+        <f>2265+463+942</f>
+        <v>3670</v>
+      </c>
+      <c r="C5" s="2">
+        <v>702.1</v>
+      </c>
+      <c r="D5">
+        <f t="shared" ref="D5:D23" si="0">C5*B5</f>
+        <v>2576707</v>
+      </c>
+      <c r="E5" s="3">
+        <f t="shared" ref="E5:E23" si="1">D5/$D$25</f>
+        <v>3.9218041743478899E-2</v>
+      </c>
+      <c r="F5"/>
+      <c r="G5"/>
+      <c r="H5"/>
+      <c r="I5"/>
+    </row>
+    <row r="6" spans="1:10" s="2" customFormat="1">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="4">
+        <f>4326+2424</f>
+        <v>6750</v>
+      </c>
+      <c r="C6" s="2">
+        <v>1801.8</v>
+      </c>
+      <c r="D6">
+        <f t="shared" si="0"/>
+        <v>12162150</v>
+      </c>
+      <c r="E6" s="3">
+        <f t="shared" si="1"/>
+        <v>0.18511057190066696</v>
+      </c>
+      <c r="F6"/>
+      <c r="G6"/>
+      <c r="H6"/>
+      <c r="I6"/>
+    </row>
+    <row r="7" spans="1:10" s="2" customFormat="1">
+      <c r="A7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="4">
+        <f>1655+330</f>
+        <v>1985</v>
+      </c>
+      <c r="C7" s="2">
+        <v>1214.9000000000001</v>
+      </c>
+      <c r="D7">
+        <f t="shared" si="0"/>
+        <v>2411576.5</v>
+      </c>
+      <c r="E7" s="3">
+        <f t="shared" si="1"/>
+        <v>3.6704719568267846E-2</v>
+      </c>
+      <c r="F7"/>
+      <c r="G7"/>
+      <c r="H7"/>
+      <c r="I7"/>
+    </row>
+    <row r="8" spans="1:10" s="2" customFormat="1">
+      <c r="A8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="4">
+        <f>448*2+37+403+478+149+306+290-604</f>
+        <v>1955</v>
+      </c>
+      <c r="C8" s="2">
+        <v>836.65</v>
+      </c>
+      <c r="D8">
+        <f t="shared" si="0"/>
+        <v>1635650.75</v>
+      </c>
+      <c r="E8" s="3">
+        <f t="shared" si="1"/>
+        <v>2.4894960657634947E-2</v>
+      </c>
+      <c r="F8"/>
+      <c r="G8" t="s">
+        <v>83</v>
+      </c>
+      <c r="H8"/>
+      <c r="I8"/>
+    </row>
+    <row r="9" spans="1:10" s="2" customFormat="1">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="4">
+        <f>1410+2189+320+59</f>
+        <v>3978</v>
+      </c>
+      <c r="C9" s="2">
+        <v>1728.2</v>
+      </c>
+      <c r="D9">
+        <f t="shared" si="0"/>
+        <v>6874779.6000000006</v>
+      </c>
+      <c r="E9" s="3">
+        <f t="shared" si="1"/>
+        <v>0.10463564283017712</v>
+      </c>
+      <c r="F9"/>
+      <c r="G9"/>
+      <c r="H9"/>
+      <c r="I9"/>
+    </row>
+    <row r="10" spans="1:10" s="2" customFormat="1">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="4">
+        <f>130+126+33+57+173+130</f>
+        <v>649</v>
+      </c>
+      <c r="C10" s="2">
+        <v>1368</v>
+      </c>
+      <c r="D10">
+        <f t="shared" si="0"/>
+        <v>887832</v>
+      </c>
+      <c r="E10" s="3">
+        <f t="shared" si="1"/>
+        <v>1.3512996408670585E-2</v>
+      </c>
+      <c r="F10"/>
+      <c r="G10"/>
+      <c r="H10"/>
+      <c r="I10"/>
+    </row>
+    <row r="11" spans="1:10" s="2" customFormat="1">
+      <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="4">
+        <f>(724+289+144+275-367)*10-3094</f>
+        <v>7556</v>
+      </c>
+      <c r="C11" s="2">
+        <v>542.5</v>
+      </c>
+      <c r="D11">
+        <f t="shared" si="0"/>
+        <v>4099130</v>
+      </c>
+      <c r="E11" s="3">
+        <f t="shared" si="1"/>
+        <v>6.2389651385255158E-2</v>
+      </c>
+      <c r="F11"/>
+      <c r="G11"/>
+      <c r="H11"/>
+      <c r="I11"/>
+    </row>
+    <row r="12" spans="1:10" s="2" customFormat="1">
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="4">
+        <f>3770+209+935+289</f>
+        <v>5203</v>
+      </c>
+      <c r="C12" s="2">
+        <v>676.95</v>
+      </c>
+      <c r="D12">
+        <f t="shared" si="0"/>
+        <v>3522170.85</v>
+      </c>
+      <c r="E12" s="3">
+        <f t="shared" si="1"/>
+        <v>5.3608207461292481E-2</v>
+      </c>
+      <c r="F12"/>
+      <c r="G12"/>
+      <c r="H12"/>
+      <c r="I12"/>
+    </row>
+    <row r="13" spans="1:10" s="2" customFormat="1">
+      <c r="A13" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" s="4">
+        <f>2434+532+562</f>
+        <v>3528</v>
+      </c>
+      <c r="C13" s="2">
+        <v>652.5</v>
+      </c>
+      <c r="D13">
+        <f t="shared" si="0"/>
+        <v>2302020</v>
+      </c>
+      <c r="E13" s="3">
+        <f t="shared" si="1"/>
+        <v>3.50372457770027E-2</v>
+      </c>
+      <c r="F13"/>
+      <c r="G13"/>
+      <c r="H13"/>
+      <c r="I13"/>
+    </row>
+    <row r="14" spans="1:10" s="2" customFormat="1">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="4">
+        <f>((840+420)*2+290+562)+3372-130-373</f>
+        <v>6241</v>
+      </c>
+      <c r="C14" s="2">
+        <v>327.2</v>
+      </c>
+      <c r="D14">
+        <f t="shared" si="0"/>
+        <v>2042055.2</v>
+      </c>
+      <c r="E14" s="3">
+        <f t="shared" si="1"/>
+        <v>3.1080524901002771E-2</v>
+      </c>
+      <c r="F14"/>
+      <c r="G14"/>
+      <c r="H14"/>
+      <c r="I14"/>
+    </row>
+    <row r="15" spans="1:10" s="2" customFormat="1">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="4">
+        <f>1280+1280+1280+910+1300+1300+2940+1300-2365+1475-2568-1840-1507</f>
+        <v>4785</v>
+      </c>
+      <c r="C15" s="2">
+        <v>157.97999999999999</v>
+      </c>
+      <c r="D15">
+        <f t="shared" si="0"/>
+        <v>755934.29999999993</v>
+      </c>
+      <c r="E15" s="3">
+        <f t="shared" si="1"/>
+        <v>1.1505484687520738E-2</v>
+      </c>
+      <c r="F15"/>
+      <c r="G15"/>
+      <c r="H15"/>
+      <c r="I15"/>
+      <c r="J15" s="5"/>
+    </row>
+    <row r="16" spans="1:10" s="2" customFormat="1">
+      <c r="A16" t="s">
+        <v>60</v>
+      </c>
+      <c r="B16" s="4">
+        <f>12359+1297</f>
+        <v>13656</v>
+      </c>
+      <c r="C16" s="2">
+        <v>78.23</v>
+      </c>
+      <c r="D16">
+        <f t="shared" si="0"/>
+        <v>1068308.8800000001</v>
+      </c>
+      <c r="E16" s="3">
+        <f t="shared" si="1"/>
+        <v>1.6259893829903515E-2</v>
+      </c>
+      <c r="F16"/>
+      <c r="G16"/>
+      <c r="H16"/>
+      <c r="I16"/>
+      <c r="J16" s="5"/>
+    </row>
+    <row r="17" spans="1:9" s="2" customFormat="1">
+      <c r="A17" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="4">
+        <f>(410+205+135+181)*2-143</f>
+        <v>1719</v>
+      </c>
+      <c r="C17" s="2">
+        <v>2692.9</v>
+      </c>
+      <c r="D17">
+        <f t="shared" si="0"/>
+        <v>4629095.1000000006</v>
+      </c>
+      <c r="E17" s="3">
+        <f t="shared" si="1"/>
+        <v>7.0455835632974043E-2</v>
+      </c>
+      <c r="F17"/>
+      <c r="G17"/>
+      <c r="H17"/>
+      <c r="I17"/>
+    </row>
+    <row r="18" spans="1:9" s="2" customFormat="1">
+      <c r="A18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" s="4">
+        <f>13763+6317+2811+3464+1538</f>
+        <v>27893</v>
+      </c>
+      <c r="C18" s="2">
+        <v>98.45</v>
+      </c>
+      <c r="D18">
+        <f t="shared" si="0"/>
+        <v>2746065.85</v>
+      </c>
+      <c r="E18" s="3">
+        <f t="shared" si="1"/>
+        <v>4.1795720326619157E-2</v>
+      </c>
+      <c r="F18"/>
+      <c r="G18"/>
+      <c r="H18"/>
+      <c r="I18"/>
+    </row>
+    <row r="19" spans="1:9" s="2" customFormat="1">
+      <c r="A19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" s="4">
+        <f>458+115+189</f>
+        <v>762</v>
+      </c>
+      <c r="C19" s="2">
+        <v>6761.5</v>
+      </c>
+      <c r="D19">
+        <f t="shared" si="0"/>
+        <v>5152263</v>
+      </c>
+      <c r="E19" s="3">
+        <f t="shared" si="1"/>
+        <v>7.841856501627148E-2</v>
+      </c>
+      <c r="F19"/>
+      <c r="G19"/>
+      <c r="H19"/>
+      <c r="I19"/>
+    </row>
+    <row r="20" spans="1:9" s="2" customFormat="1">
+      <c r="A20" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" s="4">
+        <f>(3075+1537+1153-53-1428-925-484-459-467-45+2345+1175)*2</f>
+        <v>10848</v>
+      </c>
+      <c r="C20" s="2">
+        <v>262.75</v>
+      </c>
+      <c r="D20">
+        <f t="shared" si="0"/>
+        <v>2850312</v>
+      </c>
+      <c r="E20" s="3">
+        <f t="shared" si="1"/>
+        <v>4.3382369434296887E-2</v>
+      </c>
+      <c r="F20"/>
+      <c r="G20"/>
+      <c r="H20"/>
+      <c r="I20"/>
+    </row>
+    <row r="21" spans="1:9" s="2" customFormat="1">
+      <c r="A21" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" s="4">
+        <f>7985+1084+1117+2249-5230-405-983-767-1715-339-205-937</f>
+        <v>1854</v>
+      </c>
+      <c r="C21" s="2">
+        <v>596.79999999999995</v>
+      </c>
+      <c r="D21">
+        <f t="shared" si="0"/>
+        <v>1106467.2</v>
+      </c>
+      <c r="E21" s="3">
+        <f t="shared" si="1"/>
+        <v>1.6840671771136653E-2</v>
+      </c>
+      <c r="F21"/>
+      <c r="G21"/>
+      <c r="H21"/>
+    </row>
+    <row r="22" spans="1:9" s="2" customFormat="1">
+      <c r="A22" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" s="4">
+        <f>2592+518+820</f>
+        <v>3930</v>
+      </c>
+      <c r="C22" s="2">
+        <v>1688.2</v>
+      </c>
+      <c r="D22">
+        <f t="shared" si="0"/>
+        <v>6634626</v>
+      </c>
+      <c r="E22" s="3">
+        <f t="shared" si="1"/>
+        <v>0.10098045273303112</v>
+      </c>
+      <c r="F22"/>
+      <c r="G22"/>
+      <c r="H22"/>
+      <c r="I22"/>
+    </row>
+    <row r="23" spans="1:9" s="2" customFormat="1">
+      <c r="A23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" s="4">
+        <f>40235+4295+1952-475+9018-12666-5975-9817+11418+1366-3600+5427-7979-25132+6426+17836-15111-2801-1247-5505-1765+3820-6212+5704-2774+2757-458-1307+3879-7827-231-3251+13804+4918-3138+3905</f>
+        <v>19489</v>
+      </c>
+      <c r="C23" s="2">
+        <v>115.19</v>
+      </c>
+      <c r="D23">
+        <f t="shared" si="0"/>
+        <v>2244937.91</v>
+      </c>
+      <c r="E23" s="3">
+        <f t="shared" si="1"/>
+        <v>3.4168443934796733E-2</v>
+      </c>
+      <c r="F23"/>
+      <c r="G23" t="s">
+        <v>84</v>
+      </c>
+      <c r="H23"/>
+      <c r="I23"/>
+    </row>
+    <row r="24" spans="1:9" s="2" customFormat="1">
+      <c r="A24"/>
+      <c r="B24" s="4"/>
+      <c r="D24"/>
+      <c r="E24" s="3"/>
+      <c r="F24"/>
+      <c r="G24"/>
+      <c r="H24"/>
+      <c r="I24"/>
+    </row>
+    <row r="25" spans="1:9" s="2" customFormat="1">
+      <c r="A25"/>
+      <c r="B25" s="4"/>
+      <c r="D25">
+        <f>SUM(D5:D23)</f>
+        <v>65702082.140000015</v>
+      </c>
+      <c r="E25"/>
+      <c r="F25"/>
+      <c r="G25"/>
+      <c r="H25"/>
+      <c r="I25"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup scale="77" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5540,20 +6641,20 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5562,11 +6663,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -5586,13 +6687,13 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" s="2" customFormat="1">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="B5" s="4">
         <f>2265+463</f>
@@ -5614,9 +6715,9 @@
       <c r="H5"/>
       <c r="I5"/>
     </row>
-    <row r="6" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" s="2" customFormat="1">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B6" s="4">
         <f>4326+2424</f>
@@ -5638,9 +6739,9 @@
       <c r="H6"/>
       <c r="I6"/>
     </row>
-    <row r="7" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" s="2" customFormat="1">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B7" s="4">
         <f>448*2+37+403+478+149+306+290</f>
@@ -5662,9 +6763,9 @@
       <c r="H7"/>
       <c r="I7"/>
     </row>
-    <row r="8" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" s="2" customFormat="1">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B8" s="4">
         <f>1410+2189</f>
@@ -5686,9 +6787,9 @@
       <c r="H8"/>
       <c r="I8"/>
     </row>
-    <row r="9" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" s="2" customFormat="1">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B9" s="4">
         <f>130+126+33+57+173+130</f>
@@ -5710,9 +6811,9 @@
       <c r="H9"/>
       <c r="I9"/>
     </row>
-    <row r="10" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" s="2" customFormat="1">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B10" s="4">
         <f>724+289+144+275-367</f>
@@ -5734,9 +6835,9 @@
       <c r="H10"/>
       <c r="I10"/>
     </row>
-    <row r="11" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" s="2" customFormat="1">
       <c r="A11" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B11" s="4">
         <f>3770+209+935</f>
@@ -5760,9 +6861,9 @@
       <c r="H11"/>
       <c r="I11"/>
     </row>
-    <row r="12" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" s="2" customFormat="1">
       <c r="A12" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B12" s="4">
         <f>((840+420)*2+290+562)+3372</f>
@@ -5784,9 +6885,9 @@
       <c r="H12"/>
       <c r="I12"/>
     </row>
-    <row r="13" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" s="2" customFormat="1">
       <c r="A13" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B13" s="4">
         <f>1280+1280+1280+910+1300+1300+2940+1300-2365+1475-2568</f>
@@ -5809,9 +6910,9 @@
       <c r="I13"/>
       <c r="J13" s="5"/>
     </row>
-    <row r="14" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" s="2" customFormat="1">
       <c r="A14" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B14" s="4">
         <f>(410+205+135+181)*2</f>
@@ -5833,9 +6934,9 @@
       <c r="H14"/>
       <c r="I14"/>
     </row>
-    <row r="15" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" s="2" customFormat="1">
       <c r="A15" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B15" s="4">
         <f>(1875+937+309+619)*2*2-3720</f>
@@ -5857,9 +6958,9 @@
       <c r="H15"/>
       <c r="I15"/>
     </row>
-    <row r="16" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" s="2" customFormat="1">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B16" s="4">
         <f>13763+6317+2811+3464+1538</f>
@@ -5881,9 +6982,9 @@
       <c r="H16"/>
       <c r="I16"/>
     </row>
-    <row r="17" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" s="2" customFormat="1">
       <c r="A17" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B17" s="4">
         <f>458+115+189</f>
@@ -5905,9 +7006,9 @@
       <c r="H17"/>
       <c r="I17"/>
     </row>
-    <row r="18" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" s="2" customFormat="1">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B18" s="4">
         <f>(3075+1537+1153-53-1428-925-484-459-467-45+2345+1175)*2</f>
@@ -5929,9 +7030,9 @@
       <c r="H18"/>
       <c r="I18"/>
     </row>
-    <row r="19" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" s="2" customFormat="1">
       <c r="A19" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B19" s="4">
         <f>7985+1084+1117+2249-5230-405</f>
@@ -5953,9 +7054,9 @@
       <c r="H19"/>
       <c r="I19" s="3"/>
     </row>
-    <row r="20" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" s="2" customFormat="1">
       <c r="A20" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B20" s="4">
         <f>2592+518+820</f>
@@ -5977,9 +7078,9 @@
       <c r="H20"/>
       <c r="I20"/>
     </row>
-    <row r="21" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" s="2" customFormat="1">
       <c r="A21" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B21" s="4">
         <f>40235+4295+1952-475+9018-12666-5975-9817+11418+1366-3600+5427-7979-25132+6426+17836-15111-2801-1247-5505</f>
@@ -6003,7 +7104,7 @@
       <c r="H21"/>
       <c r="I21"/>
     </row>
-    <row r="22" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" s="2" customFormat="1">
       <c r="A22"/>
       <c r="B22" s="4"/>
       <c r="D22"/>
@@ -6013,7 +7114,7 @@
       <c r="H22"/>
       <c r="I22"/>
     </row>
-    <row r="23" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" s="2" customFormat="1">
       <c r="A23"/>
       <c r="B23" s="4"/>
       <c r="D23">
@@ -6029,6 +7130,15 @@
   </sheetData>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup scale="77" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E270A1E4-8160-48C8-BABC-214DD704FB6A}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -6038,20 +7148,20 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6063,11 +7173,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -6084,13 +7194,13 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" s="2" customFormat="1">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="B5" s="4">
         <f>2265+463+942</f>
@@ -6114,9 +7224,9 @@
       <c r="H5"/>
       <c r="I5"/>
     </row>
-    <row r="6" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" s="2" customFormat="1">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B6" s="4">
         <f>4326+2424</f>
@@ -6138,9 +7248,9 @@
       <c r="H6"/>
       <c r="I6"/>
     </row>
-    <row r="7" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" s="2" customFormat="1">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B7" s="4">
         <f>448*2+37+403+478+149+306+290</f>
@@ -6162,9 +7272,9 @@
       <c r="H7"/>
       <c r="I7"/>
     </row>
-    <row r="8" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" s="2" customFormat="1">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B8" s="4">
         <f>1410+2189</f>
@@ -6186,9 +7296,9 @@
       <c r="H8"/>
       <c r="I8"/>
     </row>
-    <row r="9" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" s="2" customFormat="1">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B9" s="4">
         <f>130+126+33+57+173+130</f>
@@ -6210,9 +7320,9 @@
       <c r="H9"/>
       <c r="I9"/>
     </row>
-    <row r="10" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" s="2" customFormat="1">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B10" s="4">
         <f>724+289+144+275-367</f>
@@ -6234,9 +7344,9 @@
       <c r="H10"/>
       <c r="I10"/>
     </row>
-    <row r="11" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" s="2" customFormat="1">
       <c r="A11" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B11" s="4">
         <f>3770+209+935</f>
@@ -6258,9 +7368,9 @@
       <c r="H11"/>
       <c r="I11"/>
     </row>
-    <row r="12" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" s="2" customFormat="1">
       <c r="A12" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B12" s="4">
         <f>((840+420)*2+290+562)+3372</f>
@@ -6282,9 +7392,9 @@
       <c r="H12"/>
       <c r="I12"/>
     </row>
-    <row r="13" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" s="2" customFormat="1">
       <c r="A13" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B13" s="4">
         <f>1280+1280+1280+910+1300+1300+2940+1300-2365+1475-2568</f>
@@ -6307,9 +7417,9 @@
       <c r="I13"/>
       <c r="J13" s="5"/>
     </row>
-    <row r="14" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" s="2" customFormat="1">
       <c r="A14" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B14" s="4">
         <f>(410+205+135+181)*2</f>
@@ -6331,9 +7441,9 @@
       <c r="H14"/>
       <c r="I14"/>
     </row>
-    <row r="15" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" s="2" customFormat="1">
       <c r="A15" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B15" s="4">
         <f>(1875+937+309+619)*2*2-3720-1759</f>
@@ -6357,9 +7467,9 @@
       <c r="H15"/>
       <c r="I15"/>
     </row>
-    <row r="16" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" s="2" customFormat="1">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B16" s="4">
         <f>13763+6317+2811+3464+1538</f>
@@ -6381,9 +7491,9 @@
       <c r="H16"/>
       <c r="I16"/>
     </row>
-    <row r="17" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" s="2" customFormat="1">
       <c r="A17" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B17" s="4">
         <f>458+115+189</f>
@@ -6405,9 +7515,9 @@
       <c r="H17"/>
       <c r="I17"/>
     </row>
-    <row r="18" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" s="2" customFormat="1">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B18" s="4">
         <f>(3075+1537+1153-53-1428-925-484-459-467-45+2345+1175)*2</f>
@@ -6429,9 +7539,9 @@
       <c r="H18"/>
       <c r="I18"/>
     </row>
-    <row r="19" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" s="2" customFormat="1">
       <c r="A19" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B19" s="4">
         <f>7985+1084+1117+2249-5230-405</f>
@@ -6453,9 +7563,9 @@
       <c r="H19"/>
       <c r="I19" s="3"/>
     </row>
-    <row r="20" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" s="2" customFormat="1">
       <c r="A20" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B20" s="4">
         <f>2592+518+820</f>
@@ -6477,9 +7587,9 @@
       <c r="H20"/>
       <c r="I20"/>
     </row>
-    <row r="21" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" s="2" customFormat="1">
       <c r="A21" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B21" s="4">
         <f>40235+4295+1952-475+9018-12666-5975-9817+11418+1366-3600+5427-7979-25132+6426+17836-15111-2801-1247-5505-1765+3820-6212</f>
@@ -6503,7 +7613,7 @@
       <c r="H21"/>
       <c r="I21"/>
     </row>
-    <row r="22" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" s="2" customFormat="1">
       <c r="A22"/>
       <c r="B22" s="4"/>
       <c r="D22"/>
@@ -6513,7 +7623,7 @@
       <c r="H22"/>
       <c r="I22"/>
     </row>
-    <row r="23" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" s="2" customFormat="1">
       <c r="A23"/>
       <c r="B23" s="4"/>
       <c r="D23">
@@ -6538,20 +7648,20 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6563,11 +7673,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -6584,13 +7694,13 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" s="2" customFormat="1">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="B5" s="4">
         <f>2265+463+942</f>
@@ -6612,9 +7722,9 @@
       <c r="H5"/>
       <c r="I5"/>
     </row>
-    <row r="6" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" s="2" customFormat="1">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B6" s="4">
         <f>4326+2424</f>
@@ -6636,9 +7746,9 @@
       <c r="H6"/>
       <c r="I6"/>
     </row>
-    <row r="7" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" s="2" customFormat="1">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B7" s="4">
         <f>448*2+37+403+478+149+306+290</f>
@@ -6660,9 +7770,9 @@
       <c r="H7"/>
       <c r="I7"/>
     </row>
-    <row r="8" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" s="2" customFormat="1">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B8" s="4">
         <f>1410+2189</f>
@@ -6684,9 +7794,9 @@
       <c r="H8"/>
       <c r="I8"/>
     </row>
-    <row r="9" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" s="2" customFormat="1">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B9" s="4">
         <f>130+126+33+57+173+130</f>
@@ -6708,9 +7818,9 @@
       <c r="H9"/>
       <c r="I9"/>
     </row>
-    <row r="10" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" s="2" customFormat="1">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B10" s="4">
         <f>724+289+144+275-367</f>
@@ -6732,9 +7842,9 @@
       <c r="H10"/>
       <c r="I10"/>
     </row>
-    <row r="11" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" s="2" customFormat="1">
       <c r="A11" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B11" s="4">
         <f>3770+209+935</f>
@@ -6756,9 +7866,9 @@
       <c r="H11"/>
       <c r="I11"/>
     </row>
-    <row r="12" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" s="2" customFormat="1">
       <c r="A12" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B12" s="4">
         <f>((840+420)*2+290+562)+3372</f>
@@ -6780,9 +7890,9 @@
       <c r="H12"/>
       <c r="I12"/>
     </row>
-    <row r="13" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" s="2" customFormat="1">
       <c r="A13" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B13" s="4">
         <f>1280+1280+1280+910+1300+1300+2940+1300-2365+1475-2568</f>
@@ -6805,9 +7915,9 @@
       <c r="I13"/>
       <c r="J13" s="5"/>
     </row>
-    <row r="14" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" s="2" customFormat="1">
       <c r="A14" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B14" s="4">
         <f>(410+205+135+181)*2</f>
@@ -6829,9 +7939,9 @@
       <c r="H14"/>
       <c r="I14"/>
     </row>
-    <row r="15" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" s="2" customFormat="1">
       <c r="A15" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B15" s="4">
         <f>(1875+937+309+619)*2*2-3720-1759-2877</f>
@@ -6855,9 +7965,9 @@
       <c r="H15"/>
       <c r="I15"/>
     </row>
-    <row r="16" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" s="2" customFormat="1">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B16" s="4">
         <f>13763+6317+2811+3464+1538</f>
@@ -6879,9 +7989,9 @@
       <c r="H16"/>
       <c r="I16"/>
     </row>
-    <row r="17" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" s="2" customFormat="1">
       <c r="A17" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B17" s="4">
         <f>458+115+189</f>
@@ -6903,9 +8013,9 @@
       <c r="H17"/>
       <c r="I17"/>
     </row>
-    <row r="18" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" s="2" customFormat="1">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B18" s="4">
         <f>(3075+1537+1153-53-1428-925-484-459-467-45+2345+1175)*2</f>
@@ -6927,9 +8037,9 @@
       <c r="H18"/>
       <c r="I18"/>
     </row>
-    <row r="19" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" s="2" customFormat="1">
       <c r="A19" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B19" s="4">
         <f>7985+1084+1117+2249-5230-405</f>
@@ -6951,9 +8061,9 @@
       <c r="H19"/>
       <c r="I19" s="3"/>
     </row>
-    <row r="20" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" s="2" customFormat="1">
       <c r="A20" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B20" s="4">
         <f>2592+518+820</f>
@@ -6975,9 +8085,9 @@
       <c r="H20"/>
       <c r="I20"/>
     </row>
-    <row r="21" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" s="2" customFormat="1">
       <c r="A21" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B21" s="4">
         <f>40235+4295+1952-475+9018-12666-5975-9817+11418+1366-3600+5427-7979-25132+6426+17836-15111-2801-1247-5505-1765+3820-6212+5704</f>
@@ -7001,7 +8111,7 @@
       <c r="H21"/>
       <c r="I21"/>
     </row>
-    <row r="22" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" s="2" customFormat="1">
       <c r="A22"/>
       <c r="B22" s="4"/>
       <c r="D22"/>
@@ -7011,7 +8121,7 @@
       <c r="H22"/>
       <c r="I22"/>
     </row>
-    <row r="23" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" s="2" customFormat="1">
       <c r="A23"/>
       <c r="B23" s="4"/>
       <c r="D23">
@@ -7036,21 +8146,21 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7062,11 +8172,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -7083,13 +8193,13 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" s="2" customFormat="1">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="B5" s="4">
         <f>2265+463+942</f>
@@ -7111,9 +8221,9 @@
       <c r="H5"/>
       <c r="I5"/>
     </row>
-    <row r="6" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" s="2" customFormat="1">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B6" s="4">
         <f>4326+2424</f>
@@ -7135,9 +8245,9 @@
       <c r="H6"/>
       <c r="I6"/>
     </row>
-    <row r="7" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" s="2" customFormat="1">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B7" s="4">
         <f>448*2+37+403+478+149+306+290</f>
@@ -7159,9 +8269,9 @@
       <c r="H7"/>
       <c r="I7"/>
     </row>
-    <row r="8" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" s="2" customFormat="1">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B8" s="4">
         <f>1410+2189+320</f>
@@ -7185,9 +8295,9 @@
       <c r="H8"/>
       <c r="I8"/>
     </row>
-    <row r="9" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" s="2" customFormat="1">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B9" s="4">
         <f>130+126+33+57+173+130</f>
@@ -7209,9 +8319,9 @@
       <c r="H9"/>
       <c r="I9"/>
     </row>
-    <row r="10" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" s="2" customFormat="1">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B10" s="4">
         <f>724+289+144+275-367</f>
@@ -7233,9 +8343,9 @@
       <c r="H10"/>
       <c r="I10"/>
     </row>
-    <row r="11" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" s="2" customFormat="1">
       <c r="A11" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B11" s="4">
         <f>3770+209+935</f>
@@ -7257,9 +8367,9 @@
       <c r="H11"/>
       <c r="I11"/>
     </row>
-    <row r="12" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" s="2" customFormat="1">
       <c r="A12" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B12" s="4">
         <f>((840+420)*2+290+562)+3372</f>
@@ -7281,9 +8391,9 @@
       <c r="H12"/>
       <c r="I12"/>
     </row>
-    <row r="13" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" s="2" customFormat="1">
       <c r="A13" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B13" s="4">
         <f>1280+1280+1280+910+1300+1300+2940+1300-2365+1475-2568</f>
@@ -7306,9 +8416,9 @@
       <c r="I13"/>
       <c r="J13" s="5"/>
     </row>
-    <row r="14" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" s="2" customFormat="1">
       <c r="A14" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B14" s="4">
         <f>(410+205+135+181)*2</f>
@@ -7330,9 +8440,9 @@
       <c r="H14"/>
       <c r="I14"/>
     </row>
-    <row r="15" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" s="2" customFormat="1">
       <c r="A15" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B15" s="4">
         <f>(1875+937+309+619)*2*2-3720-1759-2877</f>
@@ -7354,9 +8464,9 @@
       <c r="H15"/>
       <c r="I15"/>
     </row>
-    <row r="16" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" s="2" customFormat="1">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B16" s="4">
         <f>13763+6317+2811+3464+1538</f>
@@ -7378,9 +8488,9 @@
       <c r="H16"/>
       <c r="I16"/>
     </row>
-    <row r="17" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" s="2" customFormat="1">
       <c r="A17" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B17" s="4">
         <f>458+115+189</f>
@@ -7402,9 +8512,9 @@
       <c r="H17"/>
       <c r="I17"/>
     </row>
-    <row r="18" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" s="2" customFormat="1">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B18" s="4">
         <f>(3075+1537+1153-53-1428-925-484-459-467-45+2345+1175)*2</f>
@@ -7426,9 +8536,9 @@
       <c r="H18"/>
       <c r="I18"/>
     </row>
-    <row r="19" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" s="2" customFormat="1">
       <c r="A19" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B19" s="4">
         <f>7985+1084+1117+2249-5230-405</f>
@@ -7450,9 +8560,9 @@
       <c r="H19"/>
       <c r="I19" s="3"/>
     </row>
-    <row r="20" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" s="2" customFormat="1">
       <c r="A20" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B20" s="4">
         <f>2592+518+820</f>
@@ -7474,9 +8584,9 @@
       <c r="H20"/>
       <c r="I20"/>
     </row>
-    <row r="21" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" s="2" customFormat="1">
       <c r="A21" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B21" s="4">
         <f>40235+4295+1952-475+9018-12666-5975-9817+11418+1366-3600+5427-7979-25132+6426+17836-15111-2801-1247-5505-1765+3820-6212+5704-2774</f>
@@ -7500,7 +8610,7 @@
       <c r="H21"/>
       <c r="I21"/>
     </row>
-    <row r="22" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" s="2" customFormat="1">
       <c r="A22"/>
       <c r="B22" s="4"/>
       <c r="D22"/>
@@ -7510,7 +8620,7 @@
       <c r="H22"/>
       <c r="I22"/>
     </row>
-    <row r="23" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" s="2" customFormat="1">
       <c r="A23"/>
       <c r="B23" s="4"/>
       <c r="D23">
@@ -7535,21 +8645,21 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7561,11 +8671,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -7582,13 +8692,13 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" s="2" customFormat="1">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="B5" s="4">
         <f>2265+463+942</f>
@@ -7610,9 +8720,9 @@
       <c r="H5"/>
       <c r="I5"/>
     </row>
-    <row r="6" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" s="2" customFormat="1">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B6" s="4">
         <f>4326+2424</f>
@@ -7634,9 +8744,9 @@
       <c r="H6"/>
       <c r="I6"/>
     </row>
-    <row r="7" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" s="2" customFormat="1">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B7" s="4">
         <f>448*2+37+403+478+149+306+290</f>
@@ -7658,9 +8768,9 @@
       <c r="H7"/>
       <c r="I7"/>
     </row>
-    <row r="8" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" s="2" customFormat="1">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B8" s="4">
         <f>1410+2189+320</f>
@@ -7682,9 +8792,9 @@
       <c r="H8"/>
       <c r="I8"/>
     </row>
-    <row r="9" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" s="2" customFormat="1">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B9" s="4">
         <f>130+126+33+57+173+130</f>
@@ -7706,9 +8816,9 @@
       <c r="H9"/>
       <c r="I9"/>
     </row>
-    <row r="10" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" s="2" customFormat="1">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B10" s="4">
         <f>724+289+144+275-367</f>
@@ -7730,9 +8840,9 @@
       <c r="H10"/>
       <c r="I10"/>
     </row>
-    <row r="11" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" s="2" customFormat="1">
       <c r="A11" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B11" s="4">
         <f>3770+209+935</f>
@@ -7754,9 +8864,9 @@
       <c r="H11"/>
       <c r="I11"/>
     </row>
-    <row r="12" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" s="2" customFormat="1">
       <c r="A12" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B12" s="4">
         <f>((840+420)*2+290+562)+3372</f>
@@ -7778,9 +8888,9 @@
       <c r="H12"/>
       <c r="I12"/>
     </row>
-    <row r="13" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" s="2" customFormat="1">
       <c r="A13" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B13" s="4">
         <f>1280+1280+1280+910+1300+1300+2940+1300-2365+1475-2568-1840</f>
@@ -7805,9 +8915,9 @@
       <c r="I13"/>
       <c r="J13" s="5"/>
     </row>
-    <row r="14" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" s="2" customFormat="1">
       <c r="A14" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B14" s="4">
         <f>(410+205+135+181)*2</f>
@@ -7829,9 +8939,9 @@
       <c r="H14"/>
       <c r="I14"/>
     </row>
-    <row r="15" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" s="2" customFormat="1">
       <c r="A15" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B15" s="4">
         <f>(1875+937+309+619)*2*2-3720-1759-2877</f>
@@ -7853,9 +8963,9 @@
       <c r="H15"/>
       <c r="I15"/>
     </row>
-    <row r="16" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" s="2" customFormat="1">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B16" s="4">
         <f>13763+6317+2811+3464+1538</f>
@@ -7877,9 +8987,9 @@
       <c r="H16"/>
       <c r="I16"/>
     </row>
-    <row r="17" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" s="2" customFormat="1">
       <c r="A17" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B17" s="4">
         <f>458+115+189</f>
@@ -7901,9 +9011,9 @@
       <c r="H17"/>
       <c r="I17"/>
     </row>
-    <row r="18" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" s="2" customFormat="1">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B18" s="4">
         <f>(3075+1537+1153-53-1428-925-484-459-467-45+2345+1175)*2</f>
@@ -7925,9 +9035,9 @@
       <c r="H18"/>
       <c r="I18"/>
     </row>
-    <row r="19" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" s="2" customFormat="1">
       <c r="A19" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B19" s="4">
         <f>7985+1084+1117+2249-5230-405</f>
@@ -7949,9 +9059,9 @@
       <c r="H19"/>
       <c r="I19" s="3"/>
     </row>
-    <row r="20" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" s="2" customFormat="1">
       <c r="A20" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B20" s="4">
         <f>2592+518+820</f>
@@ -7973,9 +9083,9 @@
       <c r="H20"/>
       <c r="I20"/>
     </row>
-    <row r="21" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" s="2" customFormat="1">
       <c r="A21" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B21" s="4">
         <f>40235+4295+1952-475+9018-12666-5975-9817+11418+1366-3600+5427-7979-25132+6426+17836-15111-2801-1247-5505-1765+3820-6212+5704-2774+2757</f>
@@ -7999,7 +9109,7 @@
       <c r="H21"/>
       <c r="I21"/>
     </row>
-    <row r="22" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" s="2" customFormat="1">
       <c r="A22"/>
       <c r="B22" s="4"/>
       <c r="D22"/>
@@ -8009,7 +9119,7 @@
       <c r="H22"/>
       <c r="I22"/>
     </row>
-    <row r="23" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" s="2" customFormat="1">
       <c r="A23"/>
       <c r="B23" s="4"/>
       <c r="D23">
@@ -8034,21 +9144,21 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8060,11 +9170,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -8081,13 +9191,13 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" s="2" customFormat="1">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="B5" s="4">
         <f>2265+463+942</f>
@@ -8109,9 +9219,9 @@
       <c r="H5"/>
       <c r="I5"/>
     </row>
-    <row r="6" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" s="2" customFormat="1">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B6" s="4">
         <f>4326+2424</f>
@@ -8133,9 +9243,9 @@
       <c r="H6"/>
       <c r="I6"/>
     </row>
-    <row r="7" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" s="2" customFormat="1">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B7" s="4">
         <f>448*2+37+403+478+149+306+290</f>
@@ -8157,9 +9267,9 @@
       <c r="H7"/>
       <c r="I7"/>
     </row>
-    <row r="8" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" s="2" customFormat="1">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B8" s="4">
         <f>1410+2189+320+59</f>
@@ -8183,9 +9293,9 @@
       <c r="H8"/>
       <c r="I8"/>
     </row>
-    <row r="9" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" s="2" customFormat="1">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B9" s="4">
         <f>130+126+33+57+173+130</f>
@@ -8207,9 +9317,9 @@
       <c r="H9"/>
       <c r="I9"/>
     </row>
-    <row r="10" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" s="2" customFormat="1">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B10" s="4">
         <f>724+289+144+275-367</f>
@@ -8231,9 +9341,9 @@
       <c r="H10"/>
       <c r="I10"/>
     </row>
-    <row r="11" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" s="2" customFormat="1">
       <c r="A11" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B11" s="4">
         <f>3770+209+935</f>
@@ -8255,9 +9365,9 @@
       <c r="H11"/>
       <c r="I11"/>
     </row>
-    <row r="12" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" s="2" customFormat="1">
       <c r="A12" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B12" s="4">
         <f>((840+420)*2+290+562)+3372</f>
@@ -8279,9 +9389,9 @@
       <c r="H12"/>
       <c r="I12"/>
     </row>
-    <row r="13" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" s="2" customFormat="1">
       <c r="A13" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B13" s="4">
         <f>1280+1280+1280+910+1300+1300+2940+1300-2365+1475-2568-1840</f>
@@ -8304,9 +9414,9 @@
       <c r="I13"/>
       <c r="J13" s="5"/>
     </row>
-    <row r="14" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" s="2" customFormat="1">
       <c r="A14" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B14" s="4">
         <f>(410+205+135+181)*2</f>
@@ -8328,9 +9438,9 @@
       <c r="H14"/>
       <c r="I14"/>
     </row>
-    <row r="15" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" s="2" customFormat="1">
       <c r="A15" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B15" s="4">
         <f>(1875+937+309+619)*2*2-3720-1759-2877</f>
@@ -8352,9 +9462,9 @@
       <c r="H15"/>
       <c r="I15"/>
     </row>
-    <row r="16" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" s="2" customFormat="1">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B16" s="4">
         <f>13763+6317+2811+3464+1538</f>
@@ -8376,9 +9486,9 @@
       <c r="H16"/>
       <c r="I16"/>
     </row>
-    <row r="17" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" s="2" customFormat="1">
       <c r="A17" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B17" s="4">
         <f>458+115+189</f>
@@ -8400,9 +9510,9 @@
       <c r="H17"/>
       <c r="I17"/>
     </row>
-    <row r="18" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" s="2" customFormat="1">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B18" s="4">
         <f>(3075+1537+1153-53-1428-925-484-459-467-45+2345+1175)*2</f>
@@ -8424,9 +9534,9 @@
       <c r="H18"/>
       <c r="I18"/>
     </row>
-    <row r="19" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" s="2" customFormat="1">
       <c r="A19" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B19" s="4">
         <f>7985+1084+1117+2249-5230-405</f>
@@ -8448,9 +9558,9 @@
       <c r="H19"/>
       <c r="I19" s="3"/>
     </row>
-    <row r="20" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" s="2" customFormat="1">
       <c r="A20" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B20" s="4">
         <f>2592+518+820</f>
@@ -8472,9 +9582,9 @@
       <c r="H20"/>
       <c r="I20"/>
     </row>
-    <row r="21" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" s="2" customFormat="1">
       <c r="A21" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B21" s="4">
         <f>40235+4295+1952-475+9018-12666-5975-9817+11418+1366-3600+5427-7979-25132+6426+17836-15111-2801-1247-5505-1765+3820-6212+5704-2774+2757-458</f>
@@ -8498,7 +9608,7 @@
       <c r="H21"/>
       <c r="I21"/>
     </row>
-    <row r="22" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" s="2" customFormat="1">
       <c r="A22"/>
       <c r="B22" s="4"/>
       <c r="D22"/>
@@ -8508,7 +9618,7 @@
       <c r="H22"/>
       <c r="I22"/>
     </row>
-    <row r="23" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" s="2" customFormat="1">
       <c r="A23"/>
       <c r="B23" s="4"/>
       <c r="D23">
@@ -8533,21 +9643,21 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8559,11 +9669,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -8580,13 +9690,13 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" s="2" customFormat="1">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="B5" s="4">
         <f>2265+463+942</f>
@@ -8608,9 +9718,9 @@
       <c r="H5"/>
       <c r="I5"/>
     </row>
-    <row r="6" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" s="2" customFormat="1">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B6" s="4">
         <f>4326+2424</f>
@@ -8632,9 +9742,9 @@
       <c r="H6"/>
       <c r="I6"/>
     </row>
-    <row r="7" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" s="2" customFormat="1">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B7" s="4">
         <f>448*2+37+403+478+149+306+290</f>
@@ -8656,9 +9766,9 @@
       <c r="H7"/>
       <c r="I7"/>
     </row>
-    <row r="8" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" s="2" customFormat="1">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B8" s="4">
         <f>1410+2189+320+59</f>
@@ -8680,9 +9790,9 @@
       <c r="H8"/>
       <c r="I8"/>
     </row>
-    <row r="9" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" s="2" customFormat="1">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B9" s="4">
         <f>130+126+33+57+173+130</f>
@@ -8704,9 +9814,9 @@
       <c r="H9"/>
       <c r="I9"/>
     </row>
-    <row r="10" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" s="2" customFormat="1">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B10" s="4">
         <f>724+289+144+275-367</f>
@@ -8728,9 +9838,9 @@
       <c r="H10"/>
       <c r="I10"/>
     </row>
-    <row r="11" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" s="2" customFormat="1">
       <c r="A11" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B11" s="4">
         <f>3770+209+935+289</f>
@@ -8749,16 +9859,16 @@
       </c>
       <c r="F11"/>
       <c r="G11" t="s">
+        <v>42</v>
+      </c>
+      <c r="H11" t="s">
         <v>43</v>
       </c>
-      <c r="H11" t="s">
-        <v>42</v>
-      </c>
       <c r="I11"/>
     </row>
-    <row r="12" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" s="2" customFormat="1">
       <c r="A12" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B12" s="4">
         <f>((840+420)*2+290+562)+3372</f>
@@ -8780,9 +9890,9 @@
       <c r="H12"/>
       <c r="I12"/>
     </row>
-    <row r="13" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" s="2" customFormat="1">
       <c r="A13" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B13" s="4">
         <f>1280+1280+1280+910+1300+1300+2940+1300-2365+1475-2568-1840</f>
@@ -8805,9 +9915,9 @@
       <c r="I13"/>
       <c r="J13" s="5"/>
     </row>
-    <row r="14" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" s="2" customFormat="1">
       <c r="A14" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B14" s="4">
         <f>(410+205+135+181)*2</f>
@@ -8829,9 +9939,9 @@
       <c r="H14"/>
       <c r="I14"/>
     </row>
-    <row r="15" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" s="2" customFormat="1">
       <c r="A15" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B15" s="4">
         <f>(1875+937+309+619)*2*2-3720-1759-2877</f>
@@ -8853,9 +9963,9 @@
       <c r="H15"/>
       <c r="I15"/>
     </row>
-    <row r="16" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" s="2" customFormat="1">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B16" s="4">
         <f>13763+6317+2811+3464+1538</f>
@@ -8877,9 +9987,9 @@
       <c r="H16"/>
       <c r="I16"/>
     </row>
-    <row r="17" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" s="2" customFormat="1">
       <c r="A17" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B17" s="4">
         <f>458+115+189</f>
@@ -8901,9 +10011,9 @@
       <c r="H17"/>
       <c r="I17"/>
     </row>
-    <row r="18" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" s="2" customFormat="1">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B18" s="4">
         <f>(3075+1537+1153-53-1428-925-484-459-467-45+2345+1175)*2</f>
@@ -8925,9 +10035,9 @@
       <c r="H18"/>
       <c r="I18"/>
     </row>
-    <row r="19" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" s="2" customFormat="1">
       <c r="A19" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B19" s="4">
         <f>7985+1084+1117+2249-5230-405</f>
@@ -8949,9 +10059,9 @@
       <c r="H19"/>
       <c r="I19" s="3"/>
     </row>
-    <row r="20" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" s="2" customFormat="1">
       <c r="A20" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B20" s="4">
         <f>2592+518+820</f>
@@ -8973,9 +10083,9 @@
       <c r="H20"/>
       <c r="I20"/>
     </row>
-    <row r="21" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" s="2" customFormat="1">
       <c r="A21" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B21" s="4">
         <f>40235+4295+1952-475+9018-12666-5975-9817+11418+1366-3600+5427-7979-25132+6426+17836-15111-2801-1247-5505-1765+3820-6212+5704-2774+2757-458-1307</f>
@@ -8999,7 +10109,7 @@
       <c r="H21"/>
       <c r="I21"/>
     </row>
-    <row r="22" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" s="2" customFormat="1">
       <c r="A22"/>
       <c r="B22" s="4"/>
       <c r="D22"/>
@@ -9009,7 +10119,7 @@
       <c r="H22"/>
       <c r="I22"/>
     </row>
-    <row r="23" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" s="2" customFormat="1">
       <c r="A23"/>
       <c r="B23" s="4"/>
       <c r="D23">
@@ -9034,21 +10144,21 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="2"/>
+    <col min="2" max="2" width="16.85546875" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" style="2"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="7" max="7" width="43.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9060,11 +10170,11 @@
       </c>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10">
       <c r="B2" s="4"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -9081,13 +10191,13 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10">
       <c r="B4" s="4"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" s="2" customFormat="1">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="B5" s="4">
         <f>2265+463+942</f>
@@ -9109,9 +10219,9 @@
       <c r="H5"/>
       <c r="I5"/>
     </row>
-    <row r="6" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" s="2" customFormat="1">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B6" s="4">
         <f>4326+2424</f>
@@ -9133,9 +10243,9 @@
       <c r="H6"/>
       <c r="I6"/>
     </row>
-    <row r="7" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" s="2" customFormat="1">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B7" s="4">
         <f>448*2+37+403+478+149+306+290</f>
@@ -9157,9 +10267,9 @@
       <c r="H7"/>
       <c r="I7"/>
     </row>
-    <row r="8" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" s="2" customFormat="1">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B8" s="4">
         <f>1410+2189+320+59</f>
@@ -9181,9 +10291,9 @@
       <c r="H8"/>
       <c r="I8"/>
     </row>
-    <row r="9" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" s="2" customFormat="1">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B9" s="4">
         <f>130+126+33+57+173+130</f>
@@ -9205,9 +10315,9 @@
       <c r="H9"/>
       <c r="I9"/>
     </row>
-    <row r="10" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" s="2" customFormat="1">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B10" s="4">
         <f>724+289+144+275-367</f>
@@ -9229,9 +10339,9 @@
       <c r="H10"/>
       <c r="I10"/>
     </row>
-    <row r="11" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" s="2" customFormat="1">
       <c r="A11" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B11" s="4">
         <f>3770+209+935+289</f>
@@ -9253,9 +10363,9 @@
       <c r="H11"/>
       <c r="I11"/>
     </row>
-    <row r="12" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" s="2" customFormat="1">
       <c r="A12" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B12" s="4">
         <f>((840+420)*2+290+562)+3372</f>
@@ -9277,9 +10387,9 @@
       <c r="H12"/>
       <c r="I12"/>
     </row>
-    <row r="13" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" s="2" customFormat="1">
       <c r="A13" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B13" s="4">
         <f>1280+1280+1280+910+1300+1300+2940+1300-2365+1475-2568-1840</f>
@@ -9302,9 +10412,9 @@
       <c r="I13"/>
       <c r="J13" s="5"/>
     </row>
-    <row r="14" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" s="2" customFormat="1">
       <c r="A14" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B14" s="4">
         <f>(410+205+135+181)*2</f>
@@ -9326,9 +10436,9 @@
       <c r="H14"/>
       <c r="I14"/>
     </row>
-    <row r="15" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" s="2" customFormat="1">
       <c r="A15" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B15" s="4">
         <f>(1875+937+309+619)*2*2-3720-1759-2877</f>
@@ -9350,9 +10460,9 @@
       <c r="H15"/>
       <c r="I15"/>
     </row>
-    <row r="16" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" s="2" customFormat="1">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B16" s="4">
         <f>13763+6317+2811+3464+1538</f>
@@ -9374,9 +10484,9 @@
       <c r="H16"/>
       <c r="I16"/>
     </row>
-    <row r="17" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" s="2" customFormat="1">
       <c r="A17" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B17" s="4">
         <f>458+115+189</f>
@@ -9398,9 +10508,9 @@
       <c r="H17"/>
       <c r="I17"/>
     </row>
-    <row r="18" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" s="2" customFormat="1">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B18" s="4">
         <f>(3075+1537+1153-53-1428-925-484-459-467-45+2345+1175)*2</f>
@@ -9422,9 +10532,9 @@
       <c r="H18"/>
       <c r="I18"/>
     </row>
-    <row r="19" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" s="2" customFormat="1">
       <c r="A19" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B19" s="4">
         <f>7985+1084+1117+2249-5230-405-983</f>
@@ -9448,9 +10558,9 @@
       <c r="H19"/>
       <c r="I19" s="3"/>
     </row>
-    <row r="20" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" s="2" customFormat="1">
       <c r="A20" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B20" s="4">
         <f>2592+518+820</f>
@@ -9472,9 +10582,9 @@
       <c r="H20"/>
       <c r="I20"/>
     </row>
-    <row r="21" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" s="2" customFormat="1">
       <c r="A21" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B21" s="4">
         <f>40235+4295+1952-475+9018-12666-5975-9817+11418+1366-3600+5427-7979-25132+6426+17836-15111-2801-1247-5505-1765+3820-6212+5704-2774+2757-458-1307+3879</f>
@@ -9498,7 +10608,7 @@
       <c r="H21"/>
       <c r="I21"/>
     </row>
-    <row r="22" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" s="2" customFormat="1">
       <c r="A22"/>
       <c r="B22" s="4"/>
       <c r="D22"/>
@@ -9508,7 +10618,7 @@
       <c r="H22"/>
       <c r="I22"/>
     </row>
-    <row r="23" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" s="2" customFormat="1">
       <c r="A23"/>
       <c r="B23" s="4"/>
       <c r="D23">
